--- a/Cronograma-2026-02-11-2026-02-28.xlsx
+++ b/Cronograma-2026-02-11-2026-02-28.xlsx
@@ -3072,6 +3072,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <conditionalFormatting sqref="C2:T30">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>C2=""</formula>
@@ -5148,7 +5149,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" formatColumns="0" formatRows="0"/>
   <conditionalFormatting sqref="B2:B34">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>TRUE</formula>

--- a/Cronograma-2026-02-11-2026-02-28.xlsx
+++ b/Cronograma-2026-02-11-2026-02-28.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="612" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="616" uniqueCount="88">
   <si>
     <t>Puestos</t>
   </si>
@@ -295,6 +295,12 @@
   </si>
   <si>
     <t>Yuri Andrea</t>
+  </si>
+  <si>
+    <t>Relleno</t>
+  </si>
+  <si>
+    <t>Relleno Noche</t>
   </si>
 </sst>
 </file>
@@ -759,75 +765,75 @@
         <v>0</v>
       </c>
       <c r="C2" cm="1">
-        <f t="array" ref="C2">_xlfn.XLOOKUP($A2,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C2">_xlfn.XLOOKUP($A2,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D2" cm="1">
-        <f t="array" ref="D2">_xlfn.XLOOKUP($A2,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D2">_xlfn.XLOOKUP($A2,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E2" cm="1">
-        <f t="array" ref="E2">_xlfn.XLOOKUP($A2,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E2">_xlfn.XLOOKUP($A2,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F2" cm="1">
-        <f t="array" ref="F2">_xlfn.XLOOKUP($A2,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F2">_xlfn.XLOOKUP($A2,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G2" cm="1">
-        <f t="array" ref="G2">_xlfn.XLOOKUP($A2,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G2">_xlfn.XLOOKUP($A2,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H2" cm="1">
-        <f t="array" ref="H2">_xlfn.XLOOKUP($A2,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H2">_xlfn.XLOOKUP($A2,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I2" cm="1">
-        <f t="array" ref="I2">_xlfn.XLOOKUP($A2,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I2">_xlfn.XLOOKUP($A2,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J2" cm="1">
-        <f t="array" ref="J2">_xlfn.XLOOKUP($A2,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J2">_xlfn.XLOOKUP($A2,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K2" cm="1">
-        <f t="array" ref="K2">_xlfn.XLOOKUP($A2,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K2">_xlfn.XLOOKUP($A2,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L2" cm="1">
-        <f t="array" ref="L2">_xlfn.XLOOKUP($A2,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L2">_xlfn.XLOOKUP($A2,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M2" cm="1">
-        <f t="array" ref="M2">_xlfn.XLOOKUP($A2,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M2">_xlfn.XLOOKUP($A2,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N2" cm="1">
-        <f t="array" ref="N2">_xlfn.XLOOKUP($A2,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N2">_xlfn.XLOOKUP($A2,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O2" cm="1">
-        <f t="array" ref="O2">_xlfn.XLOOKUP($A2,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O2">_xlfn.XLOOKUP($A2,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P2" cm="1">
-        <f t="array" ref="P2">_xlfn.XLOOKUP($A2,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P2">_xlfn.XLOOKUP($A2,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q2" cm="1">
-        <f t="array" ref="Q2">_xlfn.XLOOKUP($A2,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q2">_xlfn.XLOOKUP($A2,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R2" cm="1">
-        <f t="array" ref="R2">_xlfn.XLOOKUP($A2,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R2">_xlfn.XLOOKUP($A2,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S2" cm="1">
-        <f t="array" ref="S2">_xlfn.XLOOKUP($A2,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S2">_xlfn.XLOOKUP($A2,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T2" cm="1">
-        <f t="array" ref="T2">_xlfn.XLOOKUP($A2,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T2">_xlfn.XLOOKUP($A2,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -839,75 +845,75 @@
         <v>0</v>
       </c>
       <c r="C3" cm="1">
-        <f t="array" ref="C3">_xlfn.XLOOKUP($A3,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C3">_xlfn.XLOOKUP($A3,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D3" cm="1">
-        <f t="array" ref="D3">_xlfn.XLOOKUP($A3,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D3">_xlfn.XLOOKUP($A3,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E3" cm="1">
-        <f t="array" ref="E3">_xlfn.XLOOKUP($A3,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E3">_xlfn.XLOOKUP($A3,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F3" cm="1">
-        <f t="array" ref="F3">_xlfn.XLOOKUP($A3,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F3">_xlfn.XLOOKUP($A3,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G3" cm="1">
-        <f t="array" ref="G3">_xlfn.XLOOKUP($A3,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G3">_xlfn.XLOOKUP($A3,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H3" cm="1">
-        <f t="array" ref="H3">_xlfn.XLOOKUP($A3,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H3">_xlfn.XLOOKUP($A3,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I3" cm="1">
-        <f t="array" ref="I3">_xlfn.XLOOKUP($A3,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I3">_xlfn.XLOOKUP($A3,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J3" cm="1">
-        <f t="array" ref="J3">_xlfn.XLOOKUP($A3,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J3">_xlfn.XLOOKUP($A3,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K3" cm="1">
-        <f t="array" ref="K3">_xlfn.XLOOKUP($A3,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K3">_xlfn.XLOOKUP($A3,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L3" cm="1">
-        <f t="array" ref="L3">_xlfn.XLOOKUP($A3,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L3">_xlfn.XLOOKUP($A3,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M3" cm="1">
-        <f t="array" ref="M3">_xlfn.XLOOKUP($A3,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M3">_xlfn.XLOOKUP($A3,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N3" cm="1">
-        <f t="array" ref="N3">_xlfn.XLOOKUP($A3,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N3">_xlfn.XLOOKUP($A3,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O3" cm="1">
-        <f t="array" ref="O3">_xlfn.XLOOKUP($A3,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O3">_xlfn.XLOOKUP($A3,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P3" cm="1">
-        <f t="array" ref="P3">_xlfn.XLOOKUP($A3,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P3">_xlfn.XLOOKUP($A3,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q3" cm="1">
-        <f t="array" ref="Q3">_xlfn.XLOOKUP($A3,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q3">_xlfn.XLOOKUP($A3,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R3" cm="1">
-        <f t="array" ref="R3">_xlfn.XLOOKUP($A3,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R3">_xlfn.XLOOKUP($A3,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S3" cm="1">
-        <f t="array" ref="S3">_xlfn.XLOOKUP($A3,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S3">_xlfn.XLOOKUP($A3,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T3" cm="1">
-        <f t="array" ref="T3">_xlfn.XLOOKUP($A3,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T3">_xlfn.XLOOKUP($A3,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -919,75 +925,75 @@
         <v>0</v>
       </c>
       <c r="C4" cm="1">
-        <f t="array" ref="C4">_xlfn.XLOOKUP($A4,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C4">_xlfn.XLOOKUP($A4,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D4" cm="1">
-        <f t="array" ref="D4">_xlfn.XLOOKUP($A4,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D4">_xlfn.XLOOKUP($A4,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E4" cm="1">
-        <f t="array" ref="E4">_xlfn.XLOOKUP($A4,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E4">_xlfn.XLOOKUP($A4,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F4" cm="1">
-        <f t="array" ref="F4">_xlfn.XLOOKUP($A4,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F4">_xlfn.XLOOKUP($A4,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G4" cm="1">
-        <f t="array" ref="G4">_xlfn.XLOOKUP($A4,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G4">_xlfn.XLOOKUP($A4,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H4" cm="1">
-        <f t="array" ref="H4">_xlfn.XLOOKUP($A4,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H4">_xlfn.XLOOKUP($A4,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I4" cm="1">
-        <f t="array" ref="I4">_xlfn.XLOOKUP($A4,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I4">_xlfn.XLOOKUP($A4,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J4" cm="1">
-        <f t="array" ref="J4">_xlfn.XLOOKUP($A4,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J4">_xlfn.XLOOKUP($A4,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K4" cm="1">
-        <f t="array" ref="K4">_xlfn.XLOOKUP($A4,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K4">_xlfn.XLOOKUP($A4,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L4" cm="1">
-        <f t="array" ref="L4">_xlfn.XLOOKUP($A4,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L4">_xlfn.XLOOKUP($A4,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M4" cm="1">
-        <f t="array" ref="M4">_xlfn.XLOOKUP($A4,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M4">_xlfn.XLOOKUP($A4,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N4" cm="1">
-        <f t="array" ref="N4">_xlfn.XLOOKUP($A4,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N4">_xlfn.XLOOKUP($A4,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O4" cm="1">
-        <f t="array" ref="O4">_xlfn.XLOOKUP($A4,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O4">_xlfn.XLOOKUP($A4,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P4" cm="1">
-        <f t="array" ref="P4">_xlfn.XLOOKUP($A4,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P4">_xlfn.XLOOKUP($A4,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q4" cm="1">
-        <f t="array" ref="Q4">_xlfn.XLOOKUP($A4,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q4">_xlfn.XLOOKUP($A4,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R4" cm="1">
-        <f t="array" ref="R4">_xlfn.XLOOKUP($A4,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R4">_xlfn.XLOOKUP($A4,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S4" cm="1">
-        <f t="array" ref="S4">_xlfn.XLOOKUP($A4,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S4">_xlfn.XLOOKUP($A4,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T4" cm="1">
-        <f t="array" ref="T4">_xlfn.XLOOKUP($A4,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T4">_xlfn.XLOOKUP($A4,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -999,75 +1005,75 @@
         <v>0</v>
       </c>
       <c r="C5" cm="1">
-        <f t="array" ref="C5">_xlfn.XLOOKUP($A5,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C5">_xlfn.XLOOKUP($A5,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D5" cm="1">
-        <f t="array" ref="D5">_xlfn.XLOOKUP($A5,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D5">_xlfn.XLOOKUP($A5,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E5" cm="1">
-        <f t="array" ref="E5">_xlfn.XLOOKUP($A5,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E5">_xlfn.XLOOKUP($A5,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F5" cm="1">
-        <f t="array" ref="F5">_xlfn.XLOOKUP($A5,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F5">_xlfn.XLOOKUP($A5,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G5" cm="1">
-        <f t="array" ref="G5">_xlfn.XLOOKUP($A5,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G5">_xlfn.XLOOKUP($A5,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H5" cm="1">
-        <f t="array" ref="H5">_xlfn.XLOOKUP($A5,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H5">_xlfn.XLOOKUP($A5,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I5" cm="1">
-        <f t="array" ref="I5">_xlfn.XLOOKUP($A5,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I5">_xlfn.XLOOKUP($A5,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J5" cm="1">
-        <f t="array" ref="J5">_xlfn.XLOOKUP($A5,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J5">_xlfn.XLOOKUP($A5,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K5" cm="1">
-        <f t="array" ref="K5">_xlfn.XLOOKUP($A5,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K5">_xlfn.XLOOKUP($A5,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L5" cm="1">
-        <f t="array" ref="L5">_xlfn.XLOOKUP($A5,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L5">_xlfn.XLOOKUP($A5,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M5" cm="1">
-        <f t="array" ref="M5">_xlfn.XLOOKUP($A5,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M5">_xlfn.XLOOKUP($A5,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N5" cm="1">
-        <f t="array" ref="N5">_xlfn.XLOOKUP($A5,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N5">_xlfn.XLOOKUP($A5,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O5" cm="1">
-        <f t="array" ref="O5">_xlfn.XLOOKUP($A5,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O5">_xlfn.XLOOKUP($A5,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P5" cm="1">
-        <f t="array" ref="P5">_xlfn.XLOOKUP($A5,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P5">_xlfn.XLOOKUP($A5,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q5" cm="1">
-        <f t="array" ref="Q5">_xlfn.XLOOKUP($A5,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q5">_xlfn.XLOOKUP($A5,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R5" cm="1">
-        <f t="array" ref="R5">_xlfn.XLOOKUP($A5,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R5">_xlfn.XLOOKUP($A5,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S5" cm="1">
-        <f t="array" ref="S5">_xlfn.XLOOKUP($A5,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S5">_xlfn.XLOOKUP($A5,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T5" cm="1">
-        <f t="array" ref="T5">_xlfn.XLOOKUP($A5,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T5">_xlfn.XLOOKUP($A5,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1079,75 +1085,75 @@
         <v>0</v>
       </c>
       <c r="C6" cm="1">
-        <f t="array" ref="C6">_xlfn.XLOOKUP($A6,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C6">_xlfn.XLOOKUP($A6,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D6" cm="1">
-        <f t="array" ref="D6">_xlfn.XLOOKUP($A6,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D6">_xlfn.XLOOKUP($A6,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E6" cm="1">
-        <f t="array" ref="E6">_xlfn.XLOOKUP($A6,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E6">_xlfn.XLOOKUP($A6,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F6" cm="1">
-        <f t="array" ref="F6">_xlfn.XLOOKUP($A6,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F6">_xlfn.XLOOKUP($A6,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G6" cm="1">
-        <f t="array" ref="G6">_xlfn.XLOOKUP($A6,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G6">_xlfn.XLOOKUP($A6,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H6" cm="1">
-        <f t="array" ref="H6">_xlfn.XLOOKUP($A6,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H6">_xlfn.XLOOKUP($A6,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I6" cm="1">
-        <f t="array" ref="I6">_xlfn.XLOOKUP($A6,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I6">_xlfn.XLOOKUP($A6,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J6" cm="1">
-        <f t="array" ref="J6">_xlfn.XLOOKUP($A6,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J6">_xlfn.XLOOKUP($A6,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K6" cm="1">
-        <f t="array" ref="K6">_xlfn.XLOOKUP($A6,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K6">_xlfn.XLOOKUP($A6,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L6" cm="1">
-        <f t="array" ref="L6">_xlfn.XLOOKUP($A6,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L6">_xlfn.XLOOKUP($A6,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M6" cm="1">
-        <f t="array" ref="M6">_xlfn.XLOOKUP($A6,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M6">_xlfn.XLOOKUP($A6,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N6" cm="1">
-        <f t="array" ref="N6">_xlfn.XLOOKUP($A6,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N6">_xlfn.XLOOKUP($A6,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O6" cm="1">
-        <f t="array" ref="O6">_xlfn.XLOOKUP($A6,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O6">_xlfn.XLOOKUP($A6,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P6" cm="1">
-        <f t="array" ref="P6">_xlfn.XLOOKUP($A6,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P6">_xlfn.XLOOKUP($A6,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q6" cm="1">
-        <f t="array" ref="Q6">_xlfn.XLOOKUP($A6,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q6">_xlfn.XLOOKUP($A6,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R6" cm="1">
-        <f t="array" ref="R6">_xlfn.XLOOKUP($A6,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R6">_xlfn.XLOOKUP($A6,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S6" cm="1">
-        <f t="array" ref="S6">_xlfn.XLOOKUP($A6,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S6">_xlfn.XLOOKUP($A6,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T6" cm="1">
-        <f t="array" ref="T6">_xlfn.XLOOKUP($A6,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T6">_xlfn.XLOOKUP($A6,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1159,75 +1165,75 @@
         <v>0</v>
       </c>
       <c r="C7" cm="1">
-        <f t="array" ref="C7">_xlfn.XLOOKUP($A7,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C7">_xlfn.XLOOKUP($A7,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D7" cm="1">
-        <f t="array" ref="D7">_xlfn.XLOOKUP($A7,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D7">_xlfn.XLOOKUP($A7,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E7" cm="1">
-        <f t="array" ref="E7">_xlfn.XLOOKUP($A7,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E7">_xlfn.XLOOKUP($A7,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F7" cm="1">
-        <f t="array" ref="F7">_xlfn.XLOOKUP($A7,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F7">_xlfn.XLOOKUP($A7,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G7" cm="1">
-        <f t="array" ref="G7">_xlfn.XLOOKUP($A7,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G7">_xlfn.XLOOKUP($A7,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H7" cm="1">
-        <f t="array" ref="H7">_xlfn.XLOOKUP($A7,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H7">_xlfn.XLOOKUP($A7,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I7" cm="1">
-        <f t="array" ref="I7">_xlfn.XLOOKUP($A7,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I7">_xlfn.XLOOKUP($A7,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J7" cm="1">
-        <f t="array" ref="J7">_xlfn.XLOOKUP($A7,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J7">_xlfn.XLOOKUP($A7,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K7" cm="1">
-        <f t="array" ref="K7">_xlfn.XLOOKUP($A7,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K7">_xlfn.XLOOKUP($A7,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L7" cm="1">
-        <f t="array" ref="L7">_xlfn.XLOOKUP($A7,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L7">_xlfn.XLOOKUP($A7,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M7" cm="1">
-        <f t="array" ref="M7">_xlfn.XLOOKUP($A7,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M7">_xlfn.XLOOKUP($A7,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N7" cm="1">
-        <f t="array" ref="N7">_xlfn.XLOOKUP($A7,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N7">_xlfn.XLOOKUP($A7,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O7" cm="1">
-        <f t="array" ref="O7">_xlfn.XLOOKUP($A7,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O7">_xlfn.XLOOKUP($A7,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P7" cm="1">
-        <f t="array" ref="P7">_xlfn.XLOOKUP($A7,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P7">_xlfn.XLOOKUP($A7,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q7" cm="1">
-        <f t="array" ref="Q7">_xlfn.XLOOKUP($A7,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q7">_xlfn.XLOOKUP($A7,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R7" cm="1">
-        <f t="array" ref="R7">_xlfn.XLOOKUP($A7,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R7">_xlfn.XLOOKUP($A7,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S7" cm="1">
-        <f t="array" ref="S7">_xlfn.XLOOKUP($A7,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S7">_xlfn.XLOOKUP($A7,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T7" cm="1">
-        <f t="array" ref="T7">_xlfn.XLOOKUP($A7,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T7">_xlfn.XLOOKUP($A7,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1239,75 +1245,75 @@
         <v>0</v>
       </c>
       <c r="C8" cm="1">
-        <f t="array" ref="C8">_xlfn.XLOOKUP($A8,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C8">_xlfn.XLOOKUP($A8,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D8" cm="1">
-        <f t="array" ref="D8">_xlfn.XLOOKUP($A8,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D8">_xlfn.XLOOKUP($A8,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E8" cm="1">
-        <f t="array" ref="E8">_xlfn.XLOOKUP($A8,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E8">_xlfn.XLOOKUP($A8,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F8" cm="1">
-        <f t="array" ref="F8">_xlfn.XLOOKUP($A8,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F8">_xlfn.XLOOKUP($A8,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G8" cm="1">
-        <f t="array" ref="G8">_xlfn.XLOOKUP($A8,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G8">_xlfn.XLOOKUP($A8,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H8" cm="1">
-        <f t="array" ref="H8">_xlfn.XLOOKUP($A8,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H8">_xlfn.XLOOKUP($A8,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I8" cm="1">
-        <f t="array" ref="I8">_xlfn.XLOOKUP($A8,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I8">_xlfn.XLOOKUP($A8,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J8" cm="1">
-        <f t="array" ref="J8">_xlfn.XLOOKUP($A8,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J8">_xlfn.XLOOKUP($A8,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K8" cm="1">
-        <f t="array" ref="K8">_xlfn.XLOOKUP($A8,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K8">_xlfn.XLOOKUP($A8,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L8" cm="1">
-        <f t="array" ref="L8">_xlfn.XLOOKUP($A8,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L8">_xlfn.XLOOKUP($A8,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M8" cm="1">
-        <f t="array" ref="M8">_xlfn.XLOOKUP($A8,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M8">_xlfn.XLOOKUP($A8,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N8" cm="1">
-        <f t="array" ref="N8">_xlfn.XLOOKUP($A8,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N8">_xlfn.XLOOKUP($A8,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O8" cm="1">
-        <f t="array" ref="O8">_xlfn.XLOOKUP($A8,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O8">_xlfn.XLOOKUP($A8,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P8" cm="1">
-        <f t="array" ref="P8">_xlfn.XLOOKUP($A8,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P8">_xlfn.XLOOKUP($A8,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q8" cm="1">
-        <f t="array" ref="Q8">_xlfn.XLOOKUP($A8,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q8">_xlfn.XLOOKUP($A8,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R8" cm="1">
-        <f t="array" ref="R8">_xlfn.XLOOKUP($A8,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R8">_xlfn.XLOOKUP($A8,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S8" cm="1">
-        <f t="array" ref="S8">_xlfn.XLOOKUP($A8,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S8">_xlfn.XLOOKUP($A8,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T8" cm="1">
-        <f t="array" ref="T8">_xlfn.XLOOKUP($A8,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T8">_xlfn.XLOOKUP($A8,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1319,75 +1325,75 @@
         <v>0</v>
       </c>
       <c r="C9" cm="1">
-        <f t="array" ref="C9">_xlfn.XLOOKUP($A9,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C9">_xlfn.XLOOKUP($A9,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D9" cm="1">
-        <f t="array" ref="D9">_xlfn.XLOOKUP($A9,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D9">_xlfn.XLOOKUP($A9,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E9" cm="1">
-        <f t="array" ref="E9">_xlfn.XLOOKUP($A9,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E9">_xlfn.XLOOKUP($A9,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F9" cm="1">
-        <f t="array" ref="F9">_xlfn.XLOOKUP($A9,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F9">_xlfn.XLOOKUP($A9,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G9" cm="1">
-        <f t="array" ref="G9">_xlfn.XLOOKUP($A9,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G9">_xlfn.XLOOKUP($A9,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H9" cm="1">
-        <f t="array" ref="H9">_xlfn.XLOOKUP($A9,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H9">_xlfn.XLOOKUP($A9,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I9" cm="1">
-        <f t="array" ref="I9">_xlfn.XLOOKUP($A9,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I9">_xlfn.XLOOKUP($A9,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J9" cm="1">
-        <f t="array" ref="J9">_xlfn.XLOOKUP($A9,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J9">_xlfn.XLOOKUP($A9,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K9" cm="1">
-        <f t="array" ref="K9">_xlfn.XLOOKUP($A9,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K9">_xlfn.XLOOKUP($A9,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L9" cm="1">
-        <f t="array" ref="L9">_xlfn.XLOOKUP($A9,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L9">_xlfn.XLOOKUP($A9,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M9" cm="1">
-        <f t="array" ref="M9">_xlfn.XLOOKUP($A9,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M9">_xlfn.XLOOKUP($A9,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N9" cm="1">
-        <f t="array" ref="N9">_xlfn.XLOOKUP($A9,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N9">_xlfn.XLOOKUP($A9,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O9" cm="1">
-        <f t="array" ref="O9">_xlfn.XLOOKUP($A9,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O9">_xlfn.XLOOKUP($A9,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P9" cm="1">
-        <f t="array" ref="P9">_xlfn.XLOOKUP($A9,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P9">_xlfn.XLOOKUP($A9,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q9" cm="1">
-        <f t="array" ref="Q9">_xlfn.XLOOKUP($A9,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q9">_xlfn.XLOOKUP($A9,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R9" cm="1">
-        <f t="array" ref="R9">_xlfn.XLOOKUP($A9,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R9">_xlfn.XLOOKUP($A9,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S9" cm="1">
-        <f t="array" ref="S9">_xlfn.XLOOKUP($A9,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S9">_xlfn.XLOOKUP($A9,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T9" cm="1">
-        <f t="array" ref="T9">_xlfn.XLOOKUP($A9,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T9">_xlfn.XLOOKUP($A9,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1399,75 +1405,75 @@
         <v>0</v>
       </c>
       <c r="C10" cm="1">
-        <f t="array" ref="C10">_xlfn.XLOOKUP($A10,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C10">_xlfn.XLOOKUP($A10,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D10" cm="1">
-        <f t="array" ref="D10">_xlfn.XLOOKUP($A10,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D10">_xlfn.XLOOKUP($A10,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E10" cm="1">
-        <f t="array" ref="E10">_xlfn.XLOOKUP($A10,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E10">_xlfn.XLOOKUP($A10,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F10" cm="1">
-        <f t="array" ref="F10">_xlfn.XLOOKUP($A10,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F10">_xlfn.XLOOKUP($A10,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G10" cm="1">
-        <f t="array" ref="G10">_xlfn.XLOOKUP($A10,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G10">_xlfn.XLOOKUP($A10,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H10" cm="1">
-        <f t="array" ref="H10">_xlfn.XLOOKUP($A10,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H10">_xlfn.XLOOKUP($A10,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I10" cm="1">
-        <f t="array" ref="I10">_xlfn.XLOOKUP($A10,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I10">_xlfn.XLOOKUP($A10,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J10" cm="1">
-        <f t="array" ref="J10">_xlfn.XLOOKUP($A10,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J10">_xlfn.XLOOKUP($A10,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K10" cm="1">
-        <f t="array" ref="K10">_xlfn.XLOOKUP($A10,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K10">_xlfn.XLOOKUP($A10,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L10" cm="1">
-        <f t="array" ref="L10">_xlfn.XLOOKUP($A10,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L10">_xlfn.XLOOKUP($A10,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M10" cm="1">
-        <f t="array" ref="M10">_xlfn.XLOOKUP($A10,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M10">_xlfn.XLOOKUP($A10,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N10" cm="1">
-        <f t="array" ref="N10">_xlfn.XLOOKUP($A10,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N10">_xlfn.XLOOKUP($A10,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O10" cm="1">
-        <f t="array" ref="O10">_xlfn.XLOOKUP($A10,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O10">_xlfn.XLOOKUP($A10,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P10" cm="1">
-        <f t="array" ref="P10">_xlfn.XLOOKUP($A10,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P10">_xlfn.XLOOKUP($A10,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q10" cm="1">
-        <f t="array" ref="Q10">_xlfn.XLOOKUP($A10,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q10">_xlfn.XLOOKUP($A10,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R10" cm="1">
-        <f t="array" ref="R10">_xlfn.XLOOKUP($A10,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R10">_xlfn.XLOOKUP($A10,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S10" cm="1">
-        <f t="array" ref="S10">_xlfn.XLOOKUP($A10,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S10">_xlfn.XLOOKUP($A10,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T10" cm="1">
-        <f t="array" ref="T10">_xlfn.XLOOKUP($A10,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T10">_xlfn.XLOOKUP($A10,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1479,75 +1485,75 @@
         <v>0</v>
       </c>
       <c r="C11" cm="1">
-        <f t="array" ref="C11">_xlfn.XLOOKUP($A11,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C11">_xlfn.XLOOKUP($A11,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D11" cm="1">
-        <f t="array" ref="D11">_xlfn.XLOOKUP($A11,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D11">_xlfn.XLOOKUP($A11,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E11" cm="1">
-        <f t="array" ref="E11">_xlfn.XLOOKUP($A11,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E11">_xlfn.XLOOKUP($A11,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F11" cm="1">
-        <f t="array" ref="F11">_xlfn.XLOOKUP($A11,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F11">_xlfn.XLOOKUP($A11,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G11" cm="1">
-        <f t="array" ref="G11">_xlfn.XLOOKUP($A11,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G11">_xlfn.XLOOKUP($A11,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H11" cm="1">
-        <f t="array" ref="H11">_xlfn.XLOOKUP($A11,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H11">_xlfn.XLOOKUP($A11,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I11" cm="1">
-        <f t="array" ref="I11">_xlfn.XLOOKUP($A11,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I11">_xlfn.XLOOKUP($A11,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J11" cm="1">
-        <f t="array" ref="J11">_xlfn.XLOOKUP($A11,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J11">_xlfn.XLOOKUP($A11,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K11" cm="1">
-        <f t="array" ref="K11">_xlfn.XLOOKUP($A11,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K11">_xlfn.XLOOKUP($A11,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L11" cm="1">
-        <f t="array" ref="L11">_xlfn.XLOOKUP($A11,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L11">_xlfn.XLOOKUP($A11,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M11" cm="1">
-        <f t="array" ref="M11">_xlfn.XLOOKUP($A11,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M11">_xlfn.XLOOKUP($A11,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N11" cm="1">
-        <f t="array" ref="N11">_xlfn.XLOOKUP($A11,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N11">_xlfn.XLOOKUP($A11,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O11" cm="1">
-        <f t="array" ref="O11">_xlfn.XLOOKUP($A11,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O11">_xlfn.XLOOKUP($A11,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P11" cm="1">
-        <f t="array" ref="P11">_xlfn.XLOOKUP($A11,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P11">_xlfn.XLOOKUP($A11,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q11" cm="1">
-        <f t="array" ref="Q11">_xlfn.XLOOKUP($A11,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q11">_xlfn.XLOOKUP($A11,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R11" cm="1">
-        <f t="array" ref="R11">_xlfn.XLOOKUP($A11,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R11">_xlfn.XLOOKUP($A11,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S11" cm="1">
-        <f t="array" ref="S11">_xlfn.XLOOKUP($A11,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S11">_xlfn.XLOOKUP($A11,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T11" cm="1">
-        <f t="array" ref="T11">_xlfn.XLOOKUP($A11,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T11">_xlfn.XLOOKUP($A11,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1559,75 +1565,75 @@
         <v>0</v>
       </c>
       <c r="C12" cm="1">
-        <f t="array" ref="C12">_xlfn.XLOOKUP($A12,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C12">_xlfn.XLOOKUP($A12,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D12" cm="1">
-        <f t="array" ref="D12">_xlfn.XLOOKUP($A12,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D12">_xlfn.XLOOKUP($A12,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E12" cm="1">
-        <f t="array" ref="E12">_xlfn.XLOOKUP($A12,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E12">_xlfn.XLOOKUP($A12,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F12" cm="1">
-        <f t="array" ref="F12">_xlfn.XLOOKUP($A12,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F12">_xlfn.XLOOKUP($A12,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G12" cm="1">
-        <f t="array" ref="G12">_xlfn.XLOOKUP($A12,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G12">_xlfn.XLOOKUP($A12,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H12" cm="1">
-        <f t="array" ref="H12">_xlfn.XLOOKUP($A12,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H12">_xlfn.XLOOKUP($A12,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I12" cm="1">
-        <f t="array" ref="I12">_xlfn.XLOOKUP($A12,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I12">_xlfn.XLOOKUP($A12,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J12" cm="1">
-        <f t="array" ref="J12">_xlfn.XLOOKUP($A12,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J12">_xlfn.XLOOKUP($A12,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K12" cm="1">
-        <f t="array" ref="K12">_xlfn.XLOOKUP($A12,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K12">_xlfn.XLOOKUP($A12,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L12" cm="1">
-        <f t="array" ref="L12">_xlfn.XLOOKUP($A12,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L12">_xlfn.XLOOKUP($A12,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M12" cm="1">
-        <f t="array" ref="M12">_xlfn.XLOOKUP($A12,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M12">_xlfn.XLOOKUP($A12,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N12" cm="1">
-        <f t="array" ref="N12">_xlfn.XLOOKUP($A12,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N12">_xlfn.XLOOKUP($A12,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O12" cm="1">
-        <f t="array" ref="O12">_xlfn.XLOOKUP($A12,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O12">_xlfn.XLOOKUP($A12,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P12" cm="1">
-        <f t="array" ref="P12">_xlfn.XLOOKUP($A12,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P12">_xlfn.XLOOKUP($A12,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q12" cm="1">
-        <f t="array" ref="Q12">_xlfn.XLOOKUP($A12,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q12">_xlfn.XLOOKUP($A12,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R12" cm="1">
-        <f t="array" ref="R12">_xlfn.XLOOKUP($A12,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R12">_xlfn.XLOOKUP($A12,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S12" cm="1">
-        <f t="array" ref="S12">_xlfn.XLOOKUP($A12,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S12">_xlfn.XLOOKUP($A12,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T12" cm="1">
-        <f t="array" ref="T12">_xlfn.XLOOKUP($A12,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T12">_xlfn.XLOOKUP($A12,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1639,75 +1645,75 @@
         <v>0</v>
       </c>
       <c r="C13" cm="1">
-        <f t="array" ref="C13">_xlfn.XLOOKUP($A13,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C13">_xlfn.XLOOKUP($A13,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D13" cm="1">
-        <f t="array" ref="D13">_xlfn.XLOOKUP($A13,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D13">_xlfn.XLOOKUP($A13,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E13" cm="1">
-        <f t="array" ref="E13">_xlfn.XLOOKUP($A13,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E13">_xlfn.XLOOKUP($A13,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F13" cm="1">
-        <f t="array" ref="F13">_xlfn.XLOOKUP($A13,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F13">_xlfn.XLOOKUP($A13,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G13" cm="1">
-        <f t="array" ref="G13">_xlfn.XLOOKUP($A13,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G13">_xlfn.XLOOKUP($A13,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H13" cm="1">
-        <f t="array" ref="H13">_xlfn.XLOOKUP($A13,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H13">_xlfn.XLOOKUP($A13,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I13" cm="1">
-        <f t="array" ref="I13">_xlfn.XLOOKUP($A13,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I13">_xlfn.XLOOKUP($A13,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J13" cm="1">
-        <f t="array" ref="J13">_xlfn.XLOOKUP($A13,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J13">_xlfn.XLOOKUP($A13,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K13" cm="1">
-        <f t="array" ref="K13">_xlfn.XLOOKUP($A13,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K13">_xlfn.XLOOKUP($A13,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L13" cm="1">
-        <f t="array" ref="L13">_xlfn.XLOOKUP($A13,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L13">_xlfn.XLOOKUP($A13,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M13" cm="1">
-        <f t="array" ref="M13">_xlfn.XLOOKUP($A13,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M13">_xlfn.XLOOKUP($A13,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N13" cm="1">
-        <f t="array" ref="N13">_xlfn.XLOOKUP($A13,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N13">_xlfn.XLOOKUP($A13,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O13" cm="1">
-        <f t="array" ref="O13">_xlfn.XLOOKUP($A13,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O13">_xlfn.XLOOKUP($A13,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P13" cm="1">
-        <f t="array" ref="P13">_xlfn.XLOOKUP($A13,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P13">_xlfn.XLOOKUP($A13,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q13" cm="1">
-        <f t="array" ref="Q13">_xlfn.XLOOKUP($A13,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q13">_xlfn.XLOOKUP($A13,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R13" cm="1">
-        <f t="array" ref="R13">_xlfn.XLOOKUP($A13,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R13">_xlfn.XLOOKUP($A13,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S13" cm="1">
-        <f t="array" ref="S13">_xlfn.XLOOKUP($A13,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S13">_xlfn.XLOOKUP($A13,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T13" cm="1">
-        <f t="array" ref="T13">_xlfn.XLOOKUP($A13,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T13">_xlfn.XLOOKUP($A13,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1719,75 +1725,75 @@
         <v>0</v>
       </c>
       <c r="C14" cm="1">
-        <f t="array" ref="C14">_xlfn.XLOOKUP($A14,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C14">_xlfn.XLOOKUP($A14,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D14" cm="1">
-        <f t="array" ref="D14">_xlfn.XLOOKUP($A14,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D14">_xlfn.XLOOKUP($A14,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E14" cm="1">
-        <f t="array" ref="E14">_xlfn.XLOOKUP($A14,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E14">_xlfn.XLOOKUP($A14,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F14" cm="1">
-        <f t="array" ref="F14">_xlfn.XLOOKUP($A14,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F14">_xlfn.XLOOKUP($A14,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G14" cm="1">
-        <f t="array" ref="G14">_xlfn.XLOOKUP($A14,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G14">_xlfn.XLOOKUP($A14,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H14" cm="1">
-        <f t="array" ref="H14">_xlfn.XLOOKUP($A14,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H14">_xlfn.XLOOKUP($A14,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I14" cm="1">
-        <f t="array" ref="I14">_xlfn.XLOOKUP($A14,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I14">_xlfn.XLOOKUP($A14,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J14" cm="1">
-        <f t="array" ref="J14">_xlfn.XLOOKUP($A14,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J14">_xlfn.XLOOKUP($A14,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K14" cm="1">
-        <f t="array" ref="K14">_xlfn.XLOOKUP($A14,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K14">_xlfn.XLOOKUP($A14,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L14" cm="1">
-        <f t="array" ref="L14">_xlfn.XLOOKUP($A14,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L14">_xlfn.XLOOKUP($A14,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M14" cm="1">
-        <f t="array" ref="M14">_xlfn.XLOOKUP($A14,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M14">_xlfn.XLOOKUP($A14,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N14" cm="1">
-        <f t="array" ref="N14">_xlfn.XLOOKUP($A14,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N14">_xlfn.XLOOKUP($A14,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O14" cm="1">
-        <f t="array" ref="O14">_xlfn.XLOOKUP($A14,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O14">_xlfn.XLOOKUP($A14,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P14" cm="1">
-        <f t="array" ref="P14">_xlfn.XLOOKUP($A14,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P14">_xlfn.XLOOKUP($A14,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q14" cm="1">
-        <f t="array" ref="Q14">_xlfn.XLOOKUP($A14,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q14">_xlfn.XLOOKUP($A14,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R14" cm="1">
-        <f t="array" ref="R14">_xlfn.XLOOKUP($A14,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R14">_xlfn.XLOOKUP($A14,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S14" cm="1">
-        <f t="array" ref="S14">_xlfn.XLOOKUP($A14,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S14">_xlfn.XLOOKUP($A14,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T14" cm="1">
-        <f t="array" ref="T14">_xlfn.XLOOKUP($A14,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T14">_xlfn.XLOOKUP($A14,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1799,75 +1805,75 @@
         <v>0</v>
       </c>
       <c r="C15" cm="1">
-        <f t="array" ref="C15">_xlfn.XLOOKUP($A15,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C15">_xlfn.XLOOKUP($A15,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D15" cm="1">
-        <f t="array" ref="D15">_xlfn.XLOOKUP($A15,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D15">_xlfn.XLOOKUP($A15,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E15" cm="1">
-        <f t="array" ref="E15">_xlfn.XLOOKUP($A15,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E15">_xlfn.XLOOKUP($A15,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F15" cm="1">
-        <f t="array" ref="F15">_xlfn.XLOOKUP($A15,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F15">_xlfn.XLOOKUP($A15,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G15" cm="1">
-        <f t="array" ref="G15">_xlfn.XLOOKUP($A15,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G15">_xlfn.XLOOKUP($A15,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H15" cm="1">
-        <f t="array" ref="H15">_xlfn.XLOOKUP($A15,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H15">_xlfn.XLOOKUP($A15,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I15" cm="1">
-        <f t="array" ref="I15">_xlfn.XLOOKUP($A15,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I15">_xlfn.XLOOKUP($A15,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J15" cm="1">
-        <f t="array" ref="J15">_xlfn.XLOOKUP($A15,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J15">_xlfn.XLOOKUP($A15,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K15" cm="1">
-        <f t="array" ref="K15">_xlfn.XLOOKUP($A15,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K15">_xlfn.XLOOKUP($A15,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L15" cm="1">
-        <f t="array" ref="L15">_xlfn.XLOOKUP($A15,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L15">_xlfn.XLOOKUP($A15,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M15" cm="1">
-        <f t="array" ref="M15">_xlfn.XLOOKUP($A15,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M15">_xlfn.XLOOKUP($A15,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N15" cm="1">
-        <f t="array" ref="N15">_xlfn.XLOOKUP($A15,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N15">_xlfn.XLOOKUP($A15,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O15" cm="1">
-        <f t="array" ref="O15">_xlfn.XLOOKUP($A15,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O15">_xlfn.XLOOKUP($A15,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P15" cm="1">
-        <f t="array" ref="P15">_xlfn.XLOOKUP($A15,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P15">_xlfn.XLOOKUP($A15,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q15" cm="1">
-        <f t="array" ref="Q15">_xlfn.XLOOKUP($A15,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q15">_xlfn.XLOOKUP($A15,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R15" cm="1">
-        <f t="array" ref="R15">_xlfn.XLOOKUP($A15,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R15">_xlfn.XLOOKUP($A15,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S15" cm="1">
-        <f t="array" ref="S15">_xlfn.XLOOKUP($A15,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S15">_xlfn.XLOOKUP($A15,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T15" cm="1">
-        <f t="array" ref="T15">_xlfn.XLOOKUP($A15,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T15">_xlfn.XLOOKUP($A15,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1879,75 +1885,75 @@
         <v>0</v>
       </c>
       <c r="C16" cm="1">
-        <f t="array" ref="C16">_xlfn.XLOOKUP($A16,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C16">_xlfn.XLOOKUP($A16,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D16" cm="1">
-        <f t="array" ref="D16">_xlfn.XLOOKUP($A16,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D16">_xlfn.XLOOKUP($A16,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E16" cm="1">
-        <f t="array" ref="E16">_xlfn.XLOOKUP($A16,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E16">_xlfn.XLOOKUP($A16,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F16" cm="1">
-        <f t="array" ref="F16">_xlfn.XLOOKUP($A16,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F16">_xlfn.XLOOKUP($A16,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G16" cm="1">
-        <f t="array" ref="G16">_xlfn.XLOOKUP($A16,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G16">_xlfn.XLOOKUP($A16,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H16" cm="1">
-        <f t="array" ref="H16">_xlfn.XLOOKUP($A16,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H16">_xlfn.XLOOKUP($A16,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I16" cm="1">
-        <f t="array" ref="I16">_xlfn.XLOOKUP($A16,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I16">_xlfn.XLOOKUP($A16,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J16" cm="1">
-        <f t="array" ref="J16">_xlfn.XLOOKUP($A16,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J16">_xlfn.XLOOKUP($A16,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K16" cm="1">
-        <f t="array" ref="K16">_xlfn.XLOOKUP($A16,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K16">_xlfn.XLOOKUP($A16,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L16" cm="1">
-        <f t="array" ref="L16">_xlfn.XLOOKUP($A16,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L16">_xlfn.XLOOKUP($A16,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M16" cm="1">
-        <f t="array" ref="M16">_xlfn.XLOOKUP($A16,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M16">_xlfn.XLOOKUP($A16,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N16" cm="1">
-        <f t="array" ref="N16">_xlfn.XLOOKUP($A16,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N16">_xlfn.XLOOKUP($A16,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O16" cm="1">
-        <f t="array" ref="O16">_xlfn.XLOOKUP($A16,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O16">_xlfn.XLOOKUP($A16,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P16" cm="1">
-        <f t="array" ref="P16">_xlfn.XLOOKUP($A16,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P16">_xlfn.XLOOKUP($A16,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q16" cm="1">
-        <f t="array" ref="Q16">_xlfn.XLOOKUP($A16,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q16">_xlfn.XLOOKUP($A16,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R16" cm="1">
-        <f t="array" ref="R16">_xlfn.XLOOKUP($A16,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R16">_xlfn.XLOOKUP($A16,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S16" cm="1">
-        <f t="array" ref="S16">_xlfn.XLOOKUP($A16,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S16">_xlfn.XLOOKUP($A16,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T16" cm="1">
-        <f t="array" ref="T16">_xlfn.XLOOKUP($A16,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T16">_xlfn.XLOOKUP($A16,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -1959,75 +1965,75 @@
         <v>0</v>
       </c>
       <c r="C17" cm="1">
-        <f t="array" ref="C17">_xlfn.XLOOKUP($A17,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C17">_xlfn.XLOOKUP($A17,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D17" cm="1">
-        <f t="array" ref="D17">_xlfn.XLOOKUP($A17,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D17">_xlfn.XLOOKUP($A17,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E17" cm="1">
-        <f t="array" ref="E17">_xlfn.XLOOKUP($A17,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E17">_xlfn.XLOOKUP($A17,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F17" cm="1">
-        <f t="array" ref="F17">_xlfn.XLOOKUP($A17,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F17">_xlfn.XLOOKUP($A17,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G17" cm="1">
-        <f t="array" ref="G17">_xlfn.XLOOKUP($A17,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G17">_xlfn.XLOOKUP($A17,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H17" cm="1">
-        <f t="array" ref="H17">_xlfn.XLOOKUP($A17,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H17">_xlfn.XLOOKUP($A17,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I17" cm="1">
-        <f t="array" ref="I17">_xlfn.XLOOKUP($A17,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I17">_xlfn.XLOOKUP($A17,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J17" cm="1">
-        <f t="array" ref="J17">_xlfn.XLOOKUP($A17,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J17">_xlfn.XLOOKUP($A17,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K17" cm="1">
-        <f t="array" ref="K17">_xlfn.XLOOKUP($A17,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K17">_xlfn.XLOOKUP($A17,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L17" cm="1">
-        <f t="array" ref="L17">_xlfn.XLOOKUP($A17,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L17">_xlfn.XLOOKUP($A17,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M17" cm="1">
-        <f t="array" ref="M17">_xlfn.XLOOKUP($A17,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M17">_xlfn.XLOOKUP($A17,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N17" cm="1">
-        <f t="array" ref="N17">_xlfn.XLOOKUP($A17,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N17">_xlfn.XLOOKUP($A17,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O17" cm="1">
-        <f t="array" ref="O17">_xlfn.XLOOKUP($A17,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O17">_xlfn.XLOOKUP($A17,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P17" cm="1">
-        <f t="array" ref="P17">_xlfn.XLOOKUP($A17,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P17">_xlfn.XLOOKUP($A17,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q17" cm="1">
-        <f t="array" ref="Q17">_xlfn.XLOOKUP($A17,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q17">_xlfn.XLOOKUP($A17,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R17" cm="1">
-        <f t="array" ref="R17">_xlfn.XLOOKUP($A17,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R17">_xlfn.XLOOKUP($A17,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S17" cm="1">
-        <f t="array" ref="S17">_xlfn.XLOOKUP($A17,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S17">_xlfn.XLOOKUP($A17,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T17" cm="1">
-        <f t="array" ref="T17">_xlfn.XLOOKUP($A17,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T17">_xlfn.XLOOKUP($A17,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2039,75 +2045,75 @@
         <v>0</v>
       </c>
       <c r="C18" cm="1">
-        <f t="array" ref="C18">_xlfn.XLOOKUP($A18,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C18">_xlfn.XLOOKUP($A18,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D18" cm="1">
-        <f t="array" ref="D18">_xlfn.XLOOKUP($A18,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D18">_xlfn.XLOOKUP($A18,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E18" cm="1">
-        <f t="array" ref="E18">_xlfn.XLOOKUP($A18,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E18">_xlfn.XLOOKUP($A18,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F18" cm="1">
-        <f t="array" ref="F18">_xlfn.XLOOKUP($A18,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F18">_xlfn.XLOOKUP($A18,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G18" cm="1">
-        <f t="array" ref="G18">_xlfn.XLOOKUP($A18,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G18">_xlfn.XLOOKUP($A18,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H18" cm="1">
-        <f t="array" ref="H18">_xlfn.XLOOKUP($A18,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H18">_xlfn.XLOOKUP($A18,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I18" cm="1">
-        <f t="array" ref="I18">_xlfn.XLOOKUP($A18,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I18">_xlfn.XLOOKUP($A18,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J18" cm="1">
-        <f t="array" ref="J18">_xlfn.XLOOKUP($A18,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J18">_xlfn.XLOOKUP($A18,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K18" cm="1">
-        <f t="array" ref="K18">_xlfn.XLOOKUP($A18,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K18">_xlfn.XLOOKUP($A18,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L18" cm="1">
-        <f t="array" ref="L18">_xlfn.XLOOKUP($A18,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L18">_xlfn.XLOOKUP($A18,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M18" cm="1">
-        <f t="array" ref="M18">_xlfn.XLOOKUP($A18,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M18">_xlfn.XLOOKUP($A18,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N18" cm="1">
-        <f t="array" ref="N18">_xlfn.XLOOKUP($A18,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N18">_xlfn.XLOOKUP($A18,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O18" cm="1">
-        <f t="array" ref="O18">_xlfn.XLOOKUP($A18,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O18">_xlfn.XLOOKUP($A18,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P18" cm="1">
-        <f t="array" ref="P18">_xlfn.XLOOKUP($A18,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P18">_xlfn.XLOOKUP($A18,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q18" cm="1">
-        <f t="array" ref="Q18">_xlfn.XLOOKUP($A18,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q18">_xlfn.XLOOKUP($A18,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R18" cm="1">
-        <f t="array" ref="R18">_xlfn.XLOOKUP($A18,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R18">_xlfn.XLOOKUP($A18,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S18" cm="1">
-        <f t="array" ref="S18">_xlfn.XLOOKUP($A18,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S18">_xlfn.XLOOKUP($A18,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T18" cm="1">
-        <f t="array" ref="T18">_xlfn.XLOOKUP($A18,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T18">_xlfn.XLOOKUP($A18,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2119,75 +2125,75 @@
         <v>0</v>
       </c>
       <c r="C19" cm="1">
-        <f t="array" ref="C19">_xlfn.XLOOKUP($A19,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C19">_xlfn.XLOOKUP($A19,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D19" cm="1">
-        <f t="array" ref="D19">_xlfn.XLOOKUP($A19,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D19">_xlfn.XLOOKUP($A19,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E19" cm="1">
-        <f t="array" ref="E19">_xlfn.XLOOKUP($A19,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E19">_xlfn.XLOOKUP($A19,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F19" cm="1">
-        <f t="array" ref="F19">_xlfn.XLOOKUP($A19,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F19">_xlfn.XLOOKUP($A19,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G19" cm="1">
-        <f t="array" ref="G19">_xlfn.XLOOKUP($A19,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G19">_xlfn.XLOOKUP($A19,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H19" cm="1">
-        <f t="array" ref="H19">_xlfn.XLOOKUP($A19,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H19">_xlfn.XLOOKUP($A19,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I19" cm="1">
-        <f t="array" ref="I19">_xlfn.XLOOKUP($A19,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I19">_xlfn.XLOOKUP($A19,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J19" cm="1">
-        <f t="array" ref="J19">_xlfn.XLOOKUP($A19,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J19">_xlfn.XLOOKUP($A19,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K19" cm="1">
-        <f t="array" ref="K19">_xlfn.XLOOKUP($A19,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K19">_xlfn.XLOOKUP($A19,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L19" cm="1">
-        <f t="array" ref="L19">_xlfn.XLOOKUP($A19,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L19">_xlfn.XLOOKUP($A19,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M19" cm="1">
-        <f t="array" ref="M19">_xlfn.XLOOKUP($A19,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M19">_xlfn.XLOOKUP($A19,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N19" cm="1">
-        <f t="array" ref="N19">_xlfn.XLOOKUP($A19,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N19">_xlfn.XLOOKUP($A19,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O19" cm="1">
-        <f t="array" ref="O19">_xlfn.XLOOKUP($A19,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O19">_xlfn.XLOOKUP($A19,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P19" cm="1">
-        <f t="array" ref="P19">_xlfn.XLOOKUP($A19,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P19">_xlfn.XLOOKUP($A19,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q19" cm="1">
-        <f t="array" ref="Q19">_xlfn.XLOOKUP($A19,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q19">_xlfn.XLOOKUP($A19,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R19" cm="1">
-        <f t="array" ref="R19">_xlfn.XLOOKUP($A19,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R19">_xlfn.XLOOKUP($A19,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S19" cm="1">
-        <f t="array" ref="S19">_xlfn.XLOOKUP($A19,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S19">_xlfn.XLOOKUP($A19,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T19" cm="1">
-        <f t="array" ref="T19">_xlfn.XLOOKUP($A19,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T19">_xlfn.XLOOKUP($A19,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2199,75 +2205,75 @@
         <v>0</v>
       </c>
       <c r="C20" cm="1">
-        <f t="array" ref="C20">_xlfn.XLOOKUP($A20,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C20">_xlfn.XLOOKUP($A20,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D20" cm="1">
-        <f t="array" ref="D20">_xlfn.XLOOKUP($A20,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D20">_xlfn.XLOOKUP($A20,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E20" cm="1">
-        <f t="array" ref="E20">_xlfn.XLOOKUP($A20,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E20">_xlfn.XLOOKUP($A20,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F20" cm="1">
-        <f t="array" ref="F20">_xlfn.XLOOKUP($A20,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F20">_xlfn.XLOOKUP($A20,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G20" cm="1">
-        <f t="array" ref="G20">_xlfn.XLOOKUP($A20,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G20">_xlfn.XLOOKUP($A20,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H20" cm="1">
-        <f t="array" ref="H20">_xlfn.XLOOKUP($A20,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H20">_xlfn.XLOOKUP($A20,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I20" cm="1">
-        <f t="array" ref="I20">_xlfn.XLOOKUP($A20,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I20">_xlfn.XLOOKUP($A20,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J20" cm="1">
-        <f t="array" ref="J20">_xlfn.XLOOKUP($A20,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J20">_xlfn.XLOOKUP($A20,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K20" cm="1">
-        <f t="array" ref="K20">_xlfn.XLOOKUP($A20,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K20">_xlfn.XLOOKUP($A20,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L20" cm="1">
-        <f t="array" ref="L20">_xlfn.XLOOKUP($A20,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L20">_xlfn.XLOOKUP($A20,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M20" cm="1">
-        <f t="array" ref="M20">_xlfn.XLOOKUP($A20,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M20">_xlfn.XLOOKUP($A20,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N20" cm="1">
-        <f t="array" ref="N20">_xlfn.XLOOKUP($A20,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N20">_xlfn.XLOOKUP($A20,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O20" cm="1">
-        <f t="array" ref="O20">_xlfn.XLOOKUP($A20,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O20">_xlfn.XLOOKUP($A20,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P20" cm="1">
-        <f t="array" ref="P20">_xlfn.XLOOKUP($A20,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P20">_xlfn.XLOOKUP($A20,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q20" cm="1">
-        <f t="array" ref="Q20">_xlfn.XLOOKUP($A20,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q20">_xlfn.XLOOKUP($A20,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R20" cm="1">
-        <f t="array" ref="R20">_xlfn.XLOOKUP($A20,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R20">_xlfn.XLOOKUP($A20,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S20" cm="1">
-        <f t="array" ref="S20">_xlfn.XLOOKUP($A20,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S20">_xlfn.XLOOKUP($A20,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T20" cm="1">
-        <f t="array" ref="T20">_xlfn.XLOOKUP($A20,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T20">_xlfn.XLOOKUP($A20,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2279,75 +2285,75 @@
         <v>1</v>
       </c>
       <c r="C21" cm="1">
-        <f t="array" ref="C21">_xlfn.XLOOKUP($A21,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C21">_xlfn.XLOOKUP($A21,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D21" cm="1">
-        <f t="array" ref="D21">_xlfn.XLOOKUP($A21,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D21">_xlfn.XLOOKUP($A21,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E21" cm="1">
-        <f t="array" ref="E21">_xlfn.XLOOKUP($A21,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E21">_xlfn.XLOOKUP($A21,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F21" cm="1">
-        <f t="array" ref="F21">_xlfn.XLOOKUP($A21,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F21">_xlfn.XLOOKUP($A21,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G21" cm="1">
-        <f t="array" ref="G21">_xlfn.XLOOKUP($A21,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G21">_xlfn.XLOOKUP($A21,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H21" cm="1">
-        <f t="array" ref="H21">_xlfn.XLOOKUP($A21,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H21">_xlfn.XLOOKUP($A21,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I21" cm="1">
-        <f t="array" ref="I21">_xlfn.XLOOKUP($A21,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I21">_xlfn.XLOOKUP($A21,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J21" cm="1">
-        <f t="array" ref="J21">_xlfn.XLOOKUP($A21,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J21">_xlfn.XLOOKUP($A21,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K21" cm="1">
-        <f t="array" ref="K21">_xlfn.XLOOKUP($A21,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K21">_xlfn.XLOOKUP($A21,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L21" cm="1">
-        <f t="array" ref="L21">_xlfn.XLOOKUP($A21,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L21">_xlfn.XLOOKUP($A21,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M21" cm="1">
-        <f t="array" ref="M21">_xlfn.XLOOKUP($A21,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M21">_xlfn.XLOOKUP($A21,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N21" cm="1">
-        <f t="array" ref="N21">_xlfn.XLOOKUP($A21,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N21">_xlfn.XLOOKUP($A21,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O21" cm="1">
-        <f t="array" ref="O21">_xlfn.XLOOKUP($A21,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O21">_xlfn.XLOOKUP($A21,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P21" cm="1">
-        <f t="array" ref="P21">_xlfn.XLOOKUP($A21,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P21">_xlfn.XLOOKUP($A21,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q21" cm="1">
-        <f t="array" ref="Q21">_xlfn.XLOOKUP($A21,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q21">_xlfn.XLOOKUP($A21,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R21" cm="1">
-        <f t="array" ref="R21">_xlfn.XLOOKUP($A21,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R21">_xlfn.XLOOKUP($A21,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S21" cm="1">
-        <f t="array" ref="S21">_xlfn.XLOOKUP($A21,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S21">_xlfn.XLOOKUP($A21,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T21" cm="1">
-        <f t="array" ref="T21">_xlfn.XLOOKUP($A21,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T21">_xlfn.XLOOKUP($A21,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2359,75 +2365,75 @@
         <v>1</v>
       </c>
       <c r="C22" cm="1">
-        <f t="array" ref="C22">_xlfn.XLOOKUP($A22,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C22">_xlfn.XLOOKUP($A22,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D22" cm="1">
-        <f t="array" ref="D22">_xlfn.XLOOKUP($A22,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D22">_xlfn.XLOOKUP($A22,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E22" cm="1">
-        <f t="array" ref="E22">_xlfn.XLOOKUP($A22,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E22">_xlfn.XLOOKUP($A22,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F22" cm="1">
-        <f t="array" ref="F22">_xlfn.XLOOKUP($A22,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F22">_xlfn.XLOOKUP($A22,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G22" cm="1">
-        <f t="array" ref="G22">_xlfn.XLOOKUP($A22,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G22">_xlfn.XLOOKUP($A22,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H22" cm="1">
-        <f t="array" ref="H22">_xlfn.XLOOKUP($A22,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H22">_xlfn.XLOOKUP($A22,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I22" cm="1">
-        <f t="array" ref="I22">_xlfn.XLOOKUP($A22,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I22">_xlfn.XLOOKUP($A22,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J22" cm="1">
-        <f t="array" ref="J22">_xlfn.XLOOKUP($A22,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J22">_xlfn.XLOOKUP($A22,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K22" cm="1">
-        <f t="array" ref="K22">_xlfn.XLOOKUP($A22,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K22">_xlfn.XLOOKUP($A22,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L22" cm="1">
-        <f t="array" ref="L22">_xlfn.XLOOKUP($A22,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L22">_xlfn.XLOOKUP($A22,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M22" cm="1">
-        <f t="array" ref="M22">_xlfn.XLOOKUP($A22,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M22">_xlfn.XLOOKUP($A22,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N22" cm="1">
-        <f t="array" ref="N22">_xlfn.XLOOKUP($A22,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N22">_xlfn.XLOOKUP($A22,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O22" cm="1">
-        <f t="array" ref="O22">_xlfn.XLOOKUP($A22,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O22">_xlfn.XLOOKUP($A22,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P22" cm="1">
-        <f t="array" ref="P22">_xlfn.XLOOKUP($A22,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P22">_xlfn.XLOOKUP($A22,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q22" cm="1">
-        <f t="array" ref="Q22">_xlfn.XLOOKUP($A22,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q22">_xlfn.XLOOKUP($A22,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R22" cm="1">
-        <f t="array" ref="R22">_xlfn.XLOOKUP($A22,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R22">_xlfn.XLOOKUP($A22,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S22" cm="1">
-        <f t="array" ref="S22">_xlfn.XLOOKUP($A22,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S22">_xlfn.XLOOKUP($A22,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T22" cm="1">
-        <f t="array" ref="T22">_xlfn.XLOOKUP($A22,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T22">_xlfn.XLOOKUP($A22,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2439,75 +2445,75 @@
         <v>1</v>
       </c>
       <c r="C23" cm="1">
-        <f t="array" ref="C23">_xlfn.XLOOKUP($A23,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C23">_xlfn.XLOOKUP($A23,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D23" cm="1">
-        <f t="array" ref="D23">_xlfn.XLOOKUP($A23,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D23">_xlfn.XLOOKUP($A23,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E23" cm="1">
-        <f t="array" ref="E23">_xlfn.XLOOKUP($A23,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E23">_xlfn.XLOOKUP($A23,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F23" cm="1">
-        <f t="array" ref="F23">_xlfn.XLOOKUP($A23,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F23">_xlfn.XLOOKUP($A23,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G23" cm="1">
-        <f t="array" ref="G23">_xlfn.XLOOKUP($A23,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G23">_xlfn.XLOOKUP($A23,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H23" cm="1">
-        <f t="array" ref="H23">_xlfn.XLOOKUP($A23,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H23">_xlfn.XLOOKUP($A23,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I23" cm="1">
-        <f t="array" ref="I23">_xlfn.XLOOKUP($A23,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I23">_xlfn.XLOOKUP($A23,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J23" cm="1">
-        <f t="array" ref="J23">_xlfn.XLOOKUP($A23,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J23">_xlfn.XLOOKUP($A23,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K23" cm="1">
-        <f t="array" ref="K23">_xlfn.XLOOKUP($A23,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K23">_xlfn.XLOOKUP($A23,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L23" cm="1">
-        <f t="array" ref="L23">_xlfn.XLOOKUP($A23,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L23">_xlfn.XLOOKUP($A23,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M23" cm="1">
-        <f t="array" ref="M23">_xlfn.XLOOKUP($A23,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M23">_xlfn.XLOOKUP($A23,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N23" cm="1">
-        <f t="array" ref="N23">_xlfn.XLOOKUP($A23,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N23">_xlfn.XLOOKUP($A23,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O23" cm="1">
-        <f t="array" ref="O23">_xlfn.XLOOKUP($A23,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O23">_xlfn.XLOOKUP($A23,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P23" cm="1">
-        <f t="array" ref="P23">_xlfn.XLOOKUP($A23,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P23">_xlfn.XLOOKUP($A23,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q23" cm="1">
-        <f t="array" ref="Q23">_xlfn.XLOOKUP($A23,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q23">_xlfn.XLOOKUP($A23,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R23" cm="1">
-        <f t="array" ref="R23">_xlfn.XLOOKUP($A23,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R23">_xlfn.XLOOKUP($A23,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S23" cm="1">
-        <f t="array" ref="S23">_xlfn.XLOOKUP($A23,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S23">_xlfn.XLOOKUP($A23,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T23" cm="1">
-        <f t="array" ref="T23">_xlfn.XLOOKUP($A23,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T23">_xlfn.XLOOKUP($A23,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2519,75 +2525,75 @@
         <v>1</v>
       </c>
       <c r="C24" cm="1">
-        <f t="array" ref="C24">_xlfn.XLOOKUP($A24,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C24">_xlfn.XLOOKUP($A24,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D24" cm="1">
-        <f t="array" ref="D24">_xlfn.XLOOKUP($A24,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D24">_xlfn.XLOOKUP($A24,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E24" cm="1">
-        <f t="array" ref="E24">_xlfn.XLOOKUP($A24,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E24">_xlfn.XLOOKUP($A24,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F24" cm="1">
-        <f t="array" ref="F24">_xlfn.XLOOKUP($A24,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F24">_xlfn.XLOOKUP($A24,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G24" cm="1">
-        <f t="array" ref="G24">_xlfn.XLOOKUP($A24,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G24">_xlfn.XLOOKUP($A24,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H24" cm="1">
-        <f t="array" ref="H24">_xlfn.XLOOKUP($A24,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H24">_xlfn.XLOOKUP($A24,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I24" cm="1">
-        <f t="array" ref="I24">_xlfn.XLOOKUP($A24,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I24">_xlfn.XLOOKUP($A24,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J24" cm="1">
-        <f t="array" ref="J24">_xlfn.XLOOKUP($A24,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J24">_xlfn.XLOOKUP($A24,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K24" cm="1">
-        <f t="array" ref="K24">_xlfn.XLOOKUP($A24,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K24">_xlfn.XLOOKUP($A24,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L24" cm="1">
-        <f t="array" ref="L24">_xlfn.XLOOKUP($A24,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L24">_xlfn.XLOOKUP($A24,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M24" cm="1">
-        <f t="array" ref="M24">_xlfn.XLOOKUP($A24,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M24">_xlfn.XLOOKUP($A24,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N24" cm="1">
-        <f t="array" ref="N24">_xlfn.XLOOKUP($A24,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N24">_xlfn.XLOOKUP($A24,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O24" cm="1">
-        <f t="array" ref="O24">_xlfn.XLOOKUP($A24,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O24">_xlfn.XLOOKUP($A24,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P24" cm="1">
-        <f t="array" ref="P24">_xlfn.XLOOKUP($A24,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P24">_xlfn.XLOOKUP($A24,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q24" cm="1">
-        <f t="array" ref="Q24">_xlfn.XLOOKUP($A24,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q24">_xlfn.XLOOKUP($A24,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R24" cm="1">
-        <f t="array" ref="R24">_xlfn.XLOOKUP($A24,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R24">_xlfn.XLOOKUP($A24,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S24" cm="1">
-        <f t="array" ref="S24">_xlfn.XLOOKUP($A24,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S24">_xlfn.XLOOKUP($A24,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T24" cm="1">
-        <f t="array" ref="T24">_xlfn.XLOOKUP($A24,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T24">_xlfn.XLOOKUP($A24,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2599,75 +2605,75 @@
         <v>1</v>
       </c>
       <c r="C25" cm="1">
-        <f t="array" ref="C25">_xlfn.XLOOKUP($A25,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C25">_xlfn.XLOOKUP($A25,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D25" cm="1">
-        <f t="array" ref="D25">_xlfn.XLOOKUP($A25,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D25">_xlfn.XLOOKUP($A25,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E25" cm="1">
-        <f t="array" ref="E25">_xlfn.XLOOKUP($A25,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E25">_xlfn.XLOOKUP($A25,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F25" cm="1">
-        <f t="array" ref="F25">_xlfn.XLOOKUP($A25,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F25">_xlfn.XLOOKUP($A25,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G25" cm="1">
-        <f t="array" ref="G25">_xlfn.XLOOKUP($A25,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G25">_xlfn.XLOOKUP($A25,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H25" cm="1">
-        <f t="array" ref="H25">_xlfn.XLOOKUP($A25,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H25">_xlfn.XLOOKUP($A25,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I25" cm="1">
-        <f t="array" ref="I25">_xlfn.XLOOKUP($A25,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I25">_xlfn.XLOOKUP($A25,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J25" cm="1">
-        <f t="array" ref="J25">_xlfn.XLOOKUP($A25,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J25">_xlfn.XLOOKUP($A25,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K25" cm="1">
-        <f t="array" ref="K25">_xlfn.XLOOKUP($A25,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K25">_xlfn.XLOOKUP($A25,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L25" cm="1">
-        <f t="array" ref="L25">_xlfn.XLOOKUP($A25,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L25">_xlfn.XLOOKUP($A25,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M25" cm="1">
-        <f t="array" ref="M25">_xlfn.XLOOKUP($A25,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M25">_xlfn.XLOOKUP($A25,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N25" cm="1">
-        <f t="array" ref="N25">_xlfn.XLOOKUP($A25,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N25">_xlfn.XLOOKUP($A25,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O25" cm="1">
-        <f t="array" ref="O25">_xlfn.XLOOKUP($A25,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O25">_xlfn.XLOOKUP($A25,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P25" cm="1">
-        <f t="array" ref="P25">_xlfn.XLOOKUP($A25,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P25">_xlfn.XLOOKUP($A25,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q25" cm="1">
-        <f t="array" ref="Q25">_xlfn.XLOOKUP($A25,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q25">_xlfn.XLOOKUP($A25,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R25" cm="1">
-        <f t="array" ref="R25">_xlfn.XLOOKUP($A25,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R25">_xlfn.XLOOKUP($A25,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S25" cm="1">
-        <f t="array" ref="S25">_xlfn.XLOOKUP($A25,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S25">_xlfn.XLOOKUP($A25,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T25" cm="1">
-        <f t="array" ref="T25">_xlfn.XLOOKUP($A25,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T25">_xlfn.XLOOKUP($A25,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2679,75 +2685,75 @@
         <v>1</v>
       </c>
       <c r="C26" cm="1">
-        <f t="array" ref="C26">_xlfn.XLOOKUP($A26,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C26">_xlfn.XLOOKUP($A26,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D26" cm="1">
-        <f t="array" ref="D26">_xlfn.XLOOKUP($A26,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D26">_xlfn.XLOOKUP($A26,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E26" cm="1">
-        <f t="array" ref="E26">_xlfn.XLOOKUP($A26,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E26">_xlfn.XLOOKUP($A26,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F26" cm="1">
-        <f t="array" ref="F26">_xlfn.XLOOKUP($A26,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F26">_xlfn.XLOOKUP($A26,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G26" cm="1">
-        <f t="array" ref="G26">_xlfn.XLOOKUP($A26,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G26">_xlfn.XLOOKUP($A26,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H26" cm="1">
-        <f t="array" ref="H26">_xlfn.XLOOKUP($A26,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H26">_xlfn.XLOOKUP($A26,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I26" cm="1">
-        <f t="array" ref="I26">_xlfn.XLOOKUP($A26,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I26">_xlfn.XLOOKUP($A26,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J26" cm="1">
-        <f t="array" ref="J26">_xlfn.XLOOKUP($A26,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J26">_xlfn.XLOOKUP($A26,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K26" cm="1">
-        <f t="array" ref="K26">_xlfn.XLOOKUP($A26,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K26">_xlfn.XLOOKUP($A26,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L26" cm="1">
-        <f t="array" ref="L26">_xlfn.XLOOKUP($A26,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L26">_xlfn.XLOOKUP($A26,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M26" cm="1">
-        <f t="array" ref="M26">_xlfn.XLOOKUP($A26,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M26">_xlfn.XLOOKUP($A26,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N26" cm="1">
-        <f t="array" ref="N26">_xlfn.XLOOKUP($A26,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N26">_xlfn.XLOOKUP($A26,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O26" cm="1">
-        <f t="array" ref="O26">_xlfn.XLOOKUP($A26,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O26">_xlfn.XLOOKUP($A26,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P26" cm="1">
-        <f t="array" ref="P26">_xlfn.XLOOKUP($A26,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P26">_xlfn.XLOOKUP($A26,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q26" cm="1">
-        <f t="array" ref="Q26">_xlfn.XLOOKUP($A26,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q26">_xlfn.XLOOKUP($A26,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R26" cm="1">
-        <f t="array" ref="R26">_xlfn.XLOOKUP($A26,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R26">_xlfn.XLOOKUP($A26,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S26" cm="1">
-        <f t="array" ref="S26">_xlfn.XLOOKUP($A26,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S26">_xlfn.XLOOKUP($A26,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T26" cm="1">
-        <f t="array" ref="T26">_xlfn.XLOOKUP($A26,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T26">_xlfn.XLOOKUP($A26,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2759,75 +2765,75 @@
         <v>1</v>
       </c>
       <c r="C27" cm="1">
-        <f t="array" ref="C27">_xlfn.XLOOKUP($A27,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C27">_xlfn.XLOOKUP($A27,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D27" cm="1">
-        <f t="array" ref="D27">_xlfn.XLOOKUP($A27,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D27">_xlfn.XLOOKUP($A27,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E27" cm="1">
-        <f t="array" ref="E27">_xlfn.XLOOKUP($A27,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E27">_xlfn.XLOOKUP($A27,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F27" cm="1">
-        <f t="array" ref="F27">_xlfn.XLOOKUP($A27,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F27">_xlfn.XLOOKUP($A27,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G27" cm="1">
-        <f t="array" ref="G27">_xlfn.XLOOKUP($A27,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G27">_xlfn.XLOOKUP($A27,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H27" cm="1">
-        <f t="array" ref="H27">_xlfn.XLOOKUP($A27,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H27">_xlfn.XLOOKUP($A27,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I27" cm="1">
-        <f t="array" ref="I27">_xlfn.XLOOKUP($A27,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I27">_xlfn.XLOOKUP($A27,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J27" cm="1">
-        <f t="array" ref="J27">_xlfn.XLOOKUP($A27,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J27">_xlfn.XLOOKUP($A27,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K27" cm="1">
-        <f t="array" ref="K27">_xlfn.XLOOKUP($A27,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K27">_xlfn.XLOOKUP($A27,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L27" cm="1">
-        <f t="array" ref="L27">_xlfn.XLOOKUP($A27,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L27">_xlfn.XLOOKUP($A27,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M27" cm="1">
-        <f t="array" ref="M27">_xlfn.XLOOKUP($A27,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M27">_xlfn.XLOOKUP($A27,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N27" cm="1">
-        <f t="array" ref="N27">_xlfn.XLOOKUP($A27,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N27">_xlfn.XLOOKUP($A27,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O27" cm="1">
-        <f t="array" ref="O27">_xlfn.XLOOKUP($A27,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O27">_xlfn.XLOOKUP($A27,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P27" cm="1">
-        <f t="array" ref="P27">_xlfn.XLOOKUP($A27,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P27">_xlfn.XLOOKUP($A27,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q27" cm="1">
-        <f t="array" ref="Q27">_xlfn.XLOOKUP($A27,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q27">_xlfn.XLOOKUP($A27,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R27" cm="1">
-        <f t="array" ref="R27">_xlfn.XLOOKUP($A27,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R27">_xlfn.XLOOKUP($A27,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S27" cm="1">
-        <f t="array" ref="S27">_xlfn.XLOOKUP($A27,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S27">_xlfn.XLOOKUP($A27,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T27" cm="1">
-        <f t="array" ref="T27">_xlfn.XLOOKUP($A27,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T27">_xlfn.XLOOKUP($A27,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2839,75 +2845,75 @@
         <v>1</v>
       </c>
       <c r="C28" cm="1">
-        <f t="array" ref="C28">_xlfn.XLOOKUP($A28,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C28">_xlfn.XLOOKUP($A28,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D28" cm="1">
-        <f t="array" ref="D28">_xlfn.XLOOKUP($A28,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D28">_xlfn.XLOOKUP($A28,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E28" cm="1">
-        <f t="array" ref="E28">_xlfn.XLOOKUP($A28,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E28">_xlfn.XLOOKUP($A28,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F28" cm="1">
-        <f t="array" ref="F28">_xlfn.XLOOKUP($A28,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F28">_xlfn.XLOOKUP($A28,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G28" cm="1">
-        <f t="array" ref="G28">_xlfn.XLOOKUP($A28,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G28">_xlfn.XLOOKUP($A28,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H28" cm="1">
-        <f t="array" ref="H28">_xlfn.XLOOKUP($A28,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H28">_xlfn.XLOOKUP($A28,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I28" cm="1">
-        <f t="array" ref="I28">_xlfn.XLOOKUP($A28,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I28">_xlfn.XLOOKUP($A28,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J28" cm="1">
-        <f t="array" ref="J28">_xlfn.XLOOKUP($A28,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J28">_xlfn.XLOOKUP($A28,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K28" cm="1">
-        <f t="array" ref="K28">_xlfn.XLOOKUP($A28,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K28">_xlfn.XLOOKUP($A28,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L28" cm="1">
-        <f t="array" ref="L28">_xlfn.XLOOKUP($A28,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L28">_xlfn.XLOOKUP($A28,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M28" cm="1">
-        <f t="array" ref="M28">_xlfn.XLOOKUP($A28,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M28">_xlfn.XLOOKUP($A28,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N28" cm="1">
-        <f t="array" ref="N28">_xlfn.XLOOKUP($A28,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N28">_xlfn.XLOOKUP($A28,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O28" cm="1">
-        <f t="array" ref="O28">_xlfn.XLOOKUP($A28,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O28">_xlfn.XLOOKUP($A28,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P28" cm="1">
-        <f t="array" ref="P28">_xlfn.XLOOKUP($A28,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P28">_xlfn.XLOOKUP($A28,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q28" cm="1">
-        <f t="array" ref="Q28">_xlfn.XLOOKUP($A28,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q28">_xlfn.XLOOKUP($A28,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R28" cm="1">
-        <f t="array" ref="R28">_xlfn.XLOOKUP($A28,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R28">_xlfn.XLOOKUP($A28,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S28" cm="1">
-        <f t="array" ref="S28">_xlfn.XLOOKUP($A28,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S28">_xlfn.XLOOKUP($A28,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T28" cm="1">
-        <f t="array" ref="T28">_xlfn.XLOOKUP($A28,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T28">_xlfn.XLOOKUP($A28,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2919,75 +2925,75 @@
         <v>1</v>
       </c>
       <c r="C29" cm="1">
-        <f t="array" ref="C29">_xlfn.XLOOKUP($A29,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C29">_xlfn.XLOOKUP($A29,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D29" cm="1">
-        <f t="array" ref="D29">_xlfn.XLOOKUP($A29,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D29">_xlfn.XLOOKUP($A29,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E29" cm="1">
-        <f t="array" ref="E29">_xlfn.XLOOKUP($A29,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E29">_xlfn.XLOOKUP($A29,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F29" cm="1">
-        <f t="array" ref="F29">_xlfn.XLOOKUP($A29,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F29">_xlfn.XLOOKUP($A29,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G29" cm="1">
-        <f t="array" ref="G29">_xlfn.XLOOKUP($A29,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G29">_xlfn.XLOOKUP($A29,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H29" cm="1">
-        <f t="array" ref="H29">_xlfn.XLOOKUP($A29,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H29">_xlfn.XLOOKUP($A29,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I29" cm="1">
-        <f t="array" ref="I29">_xlfn.XLOOKUP($A29,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I29">_xlfn.XLOOKUP($A29,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J29" cm="1">
-        <f t="array" ref="J29">_xlfn.XLOOKUP($A29,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J29">_xlfn.XLOOKUP($A29,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K29" cm="1">
-        <f t="array" ref="K29">_xlfn.XLOOKUP($A29,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K29">_xlfn.XLOOKUP($A29,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L29" cm="1">
-        <f t="array" ref="L29">_xlfn.XLOOKUP($A29,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L29">_xlfn.XLOOKUP($A29,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M29" cm="1">
-        <f t="array" ref="M29">_xlfn.XLOOKUP($A29,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M29">_xlfn.XLOOKUP($A29,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N29" cm="1">
-        <f t="array" ref="N29">_xlfn.XLOOKUP($A29,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N29">_xlfn.XLOOKUP($A29,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O29" cm="1">
-        <f t="array" ref="O29">_xlfn.XLOOKUP($A29,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O29">_xlfn.XLOOKUP($A29,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P29" cm="1">
-        <f t="array" ref="P29">_xlfn.XLOOKUP($A29,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P29">_xlfn.XLOOKUP($A29,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q29" cm="1">
-        <f t="array" ref="Q29">_xlfn.XLOOKUP($A29,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q29">_xlfn.XLOOKUP($A29,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R29" cm="1">
-        <f t="array" ref="R29">_xlfn.XLOOKUP($A29,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R29">_xlfn.XLOOKUP($A29,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S29" cm="1">
-        <f t="array" ref="S29">_xlfn.XLOOKUP($A29,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S29">_xlfn.XLOOKUP($A29,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T29" cm="1">
-        <f t="array" ref="T29">_xlfn.XLOOKUP($A29,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T29">_xlfn.XLOOKUP($A29,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -2999,75 +3005,75 @@
         <v>1</v>
       </c>
       <c r="C30" cm="1">
-        <f t="array" ref="C30">_xlfn.XLOOKUP($A30,Empleados!E2:E34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="C30">_xlfn.XLOOKUP($A30,Empleados!E2:E36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="D30" cm="1">
-        <f t="array" ref="D30">_xlfn.XLOOKUP($A30,Empleados!F2:F34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="D30">_xlfn.XLOOKUP($A30,Empleados!F2:F36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="E30" cm="1">
-        <f t="array" ref="E30">_xlfn.XLOOKUP($A30,Empleados!G2:G34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="E30">_xlfn.XLOOKUP($A30,Empleados!G2:G36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="F30" cm="1">
-        <f t="array" ref="F30">_xlfn.XLOOKUP($A30,Empleados!H2:H34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="F30">_xlfn.XLOOKUP($A30,Empleados!H2:H36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="G30" cm="1">
-        <f t="array" ref="G30">_xlfn.XLOOKUP($A30,Empleados!I2:I34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="G30">_xlfn.XLOOKUP($A30,Empleados!I2:I36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="H30" cm="1">
-        <f t="array" ref="H30">_xlfn.XLOOKUP($A30,Empleados!J2:J34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="H30">_xlfn.XLOOKUP($A30,Empleados!J2:J36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="I30" cm="1">
-        <f t="array" ref="I30">_xlfn.XLOOKUP($A30,Empleados!K2:K34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="I30">_xlfn.XLOOKUP($A30,Empleados!K2:K36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="J30" cm="1">
-        <f t="array" ref="J30">_xlfn.XLOOKUP($A30,Empleados!L2:L34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="J30">_xlfn.XLOOKUP($A30,Empleados!L2:L36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="K30" cm="1">
-        <f t="array" ref="K30">_xlfn.XLOOKUP($A30,Empleados!M2:M34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="K30">_xlfn.XLOOKUP($A30,Empleados!M2:M36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="L30" cm="1">
-        <f t="array" ref="L30">_xlfn.XLOOKUP($A30,Empleados!N2:N34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="L30">_xlfn.XLOOKUP($A30,Empleados!N2:N36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="M30" cm="1">
-        <f t="array" ref="M30">_xlfn.XLOOKUP($A30,Empleados!O2:O34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="M30">_xlfn.XLOOKUP($A30,Empleados!O2:O36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="N30" cm="1">
-        <f t="array" ref="N30">_xlfn.XLOOKUP($A30,Empleados!P2:P34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="N30">_xlfn.XLOOKUP($A30,Empleados!P2:P36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="O30" cm="1">
-        <f t="array" ref="O30">_xlfn.XLOOKUP($A30,Empleados!Q2:Q34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="O30">_xlfn.XLOOKUP($A30,Empleados!Q2:Q36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="P30" cm="1">
-        <f t="array" ref="P30">_xlfn.XLOOKUP($A30,Empleados!R2:R34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="P30">_xlfn.XLOOKUP($A30,Empleados!R2:R36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="Q30" cm="1">
-        <f t="array" ref="Q30">_xlfn.XLOOKUP($A30,Empleados!S2:S34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="Q30">_xlfn.XLOOKUP($A30,Empleados!S2:S36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="R30" cm="1">
-        <f t="array" ref="R30">_xlfn.XLOOKUP($A30,Empleados!T2:T34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="R30">_xlfn.XLOOKUP($A30,Empleados!T2:T36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="S30" cm="1">
-        <f t="array" ref="S30">_xlfn.XLOOKUP($A30,Empleados!U2:U34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="S30">_xlfn.XLOOKUP($A30,Empleados!U2:U36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
       <c r="T30" cm="1">
-        <f t="array" ref="T30">_xlfn.XLOOKUP($A30,Empleados!V2:V34,Empleados!A2:A34,"")</f>
+        <f t="array" ref="T30">_xlfn.XLOOKUP($A30,Empleados!V2:V36,Empleados!A2:A36,"")</f>
         <v>0</v>
       </c>
     </row>
@@ -3084,14 +3090,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V34"/>
+  <dimension ref="A1:V36"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="4.42578125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="22" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="9" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="15" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="21" width="16.5703125" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -3179,43 +3190,43 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>41</v>
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>21</v>
       </c>
       <c r="I2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L2" t="s">
+        <v>45</v>
+      </c>
+      <c r="M2" t="s">
+        <v>45</v>
+      </c>
+      <c r="O2" t="s">
+        <v>42</v>
+      </c>
+      <c r="R2" t="s">
         <v>31</v>
-      </c>
-      <c r="J2" t="s">
-        <v>31</v>
-      </c>
-      <c r="K2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" t="s">
-        <v>31</v>
-      </c>
-      <c r="O2" t="s">
-        <v>31</v>
-      </c>
-      <c r="P2" t="s">
-        <v>21</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>34</v>
-      </c>
-      <c r="R2" t="s">
-        <v>34</v>
       </c>
       <c r="S2" t="s">
         <v>31</v>
       </c>
+      <c r="T2" t="s">
+        <v>31</v>
+      </c>
       <c r="U2" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="V2" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:22">
@@ -3238,43 +3249,37 @@
         <v>23</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" t="s">
         <v>24</v>
       </c>
       <c r="H3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="P3" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q3" t="s">
         <v>24</v>
-      </c>
-      <c r="K3" t="s">
-        <v>25</v>
-      </c>
-      <c r="L3" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>21</v>
       </c>
       <c r="R3" t="s">
         <v>21</v>
       </c>
       <c r="S3" t="s">
+        <v>23</v>
+      </c>
+      <c r="T3" t="s">
         <v>21</v>
       </c>
       <c r="V3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:22">
@@ -3308,38 +3313,35 @@
       <c r="I4" t="s">
         <v>30</v>
       </c>
-      <c r="J4" t="s">
-        <v>30</v>
-      </c>
       <c r="K4" t="s">
         <v>30</v>
       </c>
       <c r="L4" t="s">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="M4" t="s">
+        <v>30</v>
       </c>
       <c r="N4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="O4" t="s">
-        <v>28</v>
-      </c>
-      <c r="P4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="Q4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="R4" t="s">
         <v>29</v>
       </c>
+      <c r="S4" t="s">
+        <v>29</v>
+      </c>
       <c r="T4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="U4" t="s">
-        <v>28</v>
-      </c>
-      <c r="V4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:22">
@@ -3362,45 +3364,42 @@
         <v>21</v>
       </c>
       <c r="F5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="G5" t="s">
         <v>25</v>
       </c>
       <c r="H5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I5" t="s">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="J5" t="s">
+        <v>45</v>
       </c>
       <c r="K5" t="s">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="L5" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="M5" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="N5" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" t="s">
-        <v>23</v>
+        <v>39</v>
+      </c>
+      <c r="P5" t="s">
+        <v>42</v>
       </c>
       <c r="Q5" t="s">
+        <v>43</v>
+      </c>
+      <c r="R5" t="s">
         <v>45</v>
       </c>
-      <c r="R5" t="s">
-        <v>44</v>
-      </c>
       <c r="S5" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="T5" t="s">
-        <v>42</v>
-      </c>
-      <c r="U5" t="s">
         <v>43</v>
       </c>
     </row>
@@ -3435,38 +3434,35 @@
       <c r="I6" t="s">
         <v>35</v>
       </c>
-      <c r="J6" t="s">
-        <v>35</v>
-      </c>
       <c r="K6" t="s">
         <v>35</v>
       </c>
       <c r="L6" t="s">
         <v>35</v>
       </c>
+      <c r="M6" t="s">
+        <v>35</v>
+      </c>
       <c r="N6" t="s">
         <v>35</v>
       </c>
       <c r="O6" t="s">
         <v>35</v>
       </c>
-      <c r="P6" t="s">
-        <v>35</v>
-      </c>
       <c r="Q6" t="s">
         <v>35</v>
       </c>
       <c r="R6" t="s">
         <v>35</v>
       </c>
+      <c r="S6" t="s">
+        <v>35</v>
+      </c>
       <c r="T6" t="s">
         <v>35</v>
       </c>
       <c r="U6" t="s">
-        <v>35</v>
-      </c>
-      <c r="V6" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:22">
@@ -3500,20 +3496,23 @@
       <c r="I7" t="s">
         <v>47</v>
       </c>
-      <c r="K7" t="s">
-        <v>47</v>
-      </c>
       <c r="L7" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="M7" t="s">
-        <v>47</v>
+        <v>34</v>
+      </c>
+      <c r="N7" t="s">
+        <v>34</v>
       </c>
       <c r="O7" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="P7" t="s">
-        <v>47</v>
+        <v>34</v>
+      </c>
+      <c r="R7" t="s">
+        <v>34</v>
       </c>
       <c r="S7" t="s">
         <v>34</v>
@@ -3547,41 +3546,44 @@
       <c r="E8" t="s">
         <v>39</v>
       </c>
-      <c r="F8" t="s">
-        <v>39</v>
-      </c>
-      <c r="G8" t="s">
-        <v>39</v>
-      </c>
       <c r="H8" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="I8" t="s">
-        <v>39</v>
+        <v>21</v>
+      </c>
+      <c r="J8" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" t="s">
+        <v>24</v>
       </c>
       <c r="L8" t="s">
-        <v>39</v>
-      </c>
-      <c r="M8" t="s">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="N8" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="O8" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="P8" t="s">
+        <v>41</v>
       </c>
       <c r="Q8" t="s">
-        <v>39</v>
+        <v>44</v>
+      </c>
+      <c r="R8" t="s">
+        <v>40</v>
       </c>
       <c r="T8" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="U8" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="V8" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:22">
@@ -3601,25 +3603,22 @@
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="I9" t="s">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="J9" t="s">
-        <v>41</v>
+        <v>20</v>
+      </c>
+      <c r="K9" t="s">
+        <v>25</v>
       </c>
       <c r="L9" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="M9" t="s">
-        <v>45</v>
-      </c>
-      <c r="N9" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="O9" t="s">
         <v>45</v>
@@ -3627,14 +3626,20 @@
       <c r="P9" t="s">
         <v>45</v>
       </c>
+      <c r="Q9" t="s">
+        <v>41</v>
+      </c>
       <c r="R9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="S9" t="s">
-        <v>39</v>
-      </c>
-      <c r="T9" t="s">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="U9" t="s">
+        <v>43</v>
+      </c>
+      <c r="V9" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -3654,49 +3659,49 @@
         <v>0</v>
       </c>
       <c r="E10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" t="s">
+        <v>32</v>
+      </c>
+      <c r="G10" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10" t="s">
         <v>48</v>
       </c>
-      <c r="F10" t="s">
+      <c r="L10" t="s">
         <v>48</v>
       </c>
-      <c r="G10" t="s">
+      <c r="M10" t="s">
         <v>48</v>
       </c>
-      <c r="H10" t="s">
+      <c r="N10" t="s">
         <v>48</v>
       </c>
-      <c r="I10" t="s">
+      <c r="O10" t="s">
         <v>48</v>
       </c>
-      <c r="K10" t="s">
-        <v>32</v>
-      </c>
-      <c r="L10" t="s">
-        <v>32</v>
-      </c>
-      <c r="N10" t="s">
-        <v>32</v>
-      </c>
-      <c r="O10" t="s">
-        <v>32</v>
-      </c>
-      <c r="P10" t="s">
-        <v>32</v>
-      </c>
       <c r="Q10" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="R10" t="s">
-        <v>32</v>
+        <v>48</v>
+      </c>
+      <c r="S10" t="s">
+        <v>48</v>
       </c>
       <c r="T10" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="U10" t="s">
-        <v>32</v>
-      </c>
-      <c r="V10" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -3718,44 +3723,44 @@
       <c r="E11" t="s">
         <v>25</v>
       </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
       <c r="G11" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" t="s">
+        <v>23</v>
+      </c>
+      <c r="J11" t="s">
         <v>41</v>
       </c>
-      <c r="H11" t="s">
+      <c r="K11" t="s">
         <v>41</v>
       </c>
-      <c r="I11" t="s">
+      <c r="L11" t="s">
+        <v>39</v>
+      </c>
+      <c r="M11" t="s">
+        <v>39</v>
+      </c>
+      <c r="N11" t="s">
         <v>41</v>
       </c>
-      <c r="J11" t="s">
-        <v>44</v>
-      </c>
-      <c r="K11" t="s">
-        <v>40</v>
-      </c>
-      <c r="M11" t="s">
+      <c r="P11" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>39</v>
+      </c>
+      <c r="R11" t="s">
+        <v>39</v>
+      </c>
+      <c r="S11" t="s">
         <v>41</v>
       </c>
-      <c r="N11" t="s">
-        <v>45</v>
-      </c>
-      <c r="O11" t="s">
-        <v>41</v>
-      </c>
-      <c r="P11" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>43</v>
-      </c>
       <c r="T11" t="s">
-        <v>24</v>
-      </c>
-      <c r="U11" t="s">
-        <v>23</v>
-      </c>
-      <c r="V11" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -3789,20 +3794,20 @@
       <c r="I12" t="s">
         <v>28</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>28</v>
       </c>
-      <c r="K12" t="s">
-        <v>46</v>
-      </c>
       <c r="L12" t="s">
+        <v>28</v>
+      </c>
+      <c r="M12" t="s">
         <v>29</v>
       </c>
-      <c r="M12" t="s">
-        <v>46</v>
-      </c>
-      <c r="P12" t="s">
+      <c r="N12" t="s">
         <v>28</v>
+      </c>
+      <c r="O12" t="s">
+        <v>29</v>
       </c>
       <c r="Q12" t="s">
         <v>28</v>
@@ -3811,13 +3816,13 @@
         <v>28</v>
       </c>
       <c r="S12" t="s">
-        <v>46</v>
+        <v>28</v>
+      </c>
+      <c r="T12" t="s">
+        <v>28</v>
       </c>
       <c r="U12" t="s">
-        <v>46</v>
-      </c>
-      <c r="V12" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -3851,9 +3856,6 @@
       <c r="I13" t="s">
         <v>37</v>
       </c>
-      <c r="J13" t="s">
-        <v>37</v>
-      </c>
       <c r="K13" t="s">
         <v>37</v>
       </c>
@@ -3869,9 +3871,6 @@
       <c r="O13" t="s">
         <v>37</v>
       </c>
-      <c r="P13" t="s">
-        <v>37</v>
-      </c>
       <c r="Q13" t="s">
         <v>37</v>
       </c>
@@ -3885,9 +3884,6 @@
         <v>37</v>
       </c>
       <c r="U13" t="s">
-        <v>37</v>
-      </c>
-      <c r="V13" t="s">
         <v>37</v>
       </c>
     </row>
@@ -3910,47 +3906,44 @@
       <c r="E14" t="s">
         <v>24</v>
       </c>
-      <c r="F14" t="s">
-        <v>25</v>
-      </c>
       <c r="G14" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="H14" t="s">
-        <v>23</v>
+        <v>41</v>
+      </c>
+      <c r="I14" t="s">
+        <v>43</v>
       </c>
       <c r="J14" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K14" t="s">
-        <v>43</v>
-      </c>
-      <c r="L14" t="s">
         <v>45</v>
       </c>
-      <c r="M14" t="s">
-        <v>44</v>
-      </c>
       <c r="N14" t="s">
-        <v>43</v>
+        <v>26</v>
+      </c>
+      <c r="O14" t="s">
+        <v>20</v>
       </c>
       <c r="P14" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="Q14" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="R14" t="s">
-        <v>39</v>
-      </c>
-      <c r="S14" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="T14" t="s">
-        <v>40</v>
+        <v>24</v>
+      </c>
+      <c r="U14" t="s">
+        <v>24</v>
       </c>
       <c r="V14" t="s">
-        <v>39</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3987,18 +3980,9 @@
       <c r="K15" t="s">
         <v>20</v>
       </c>
-      <c r="L15" t="s">
-        <v>20</v>
-      </c>
-      <c r="M15" t="s">
-        <v>20</v>
-      </c>
       <c r="N15" t="s">
         <v>20</v>
       </c>
-      <c r="O15" t="s">
-        <v>20</v>
-      </c>
       <c r="Q15" t="s">
         <v>20</v>
       </c>
@@ -4006,6 +3990,9 @@
         <v>20</v>
       </c>
       <c r="S15" t="s">
+        <v>20</v>
+      </c>
+      <c r="T15" t="s">
         <v>20</v>
       </c>
       <c r="U15" t="s">
@@ -4029,52 +4016,46 @@
         <v>0</v>
       </c>
       <c r="E16" t="s">
-        <v>33</v>
-      </c>
-      <c r="F16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G16" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="H16" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="I16" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="J16" t="s">
-        <v>33</v>
-      </c>
-      <c r="L16" t="s">
-        <v>33</v>
-      </c>
-      <c r="M16" t="s">
-        <v>33</v>
+        <v>43</v>
+      </c>
+      <c r="K16" t="s">
+        <v>44</v>
       </c>
       <c r="N16" t="s">
         <v>33</v>
       </c>
       <c r="O16" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="P16" t="s">
         <v>31</v>
       </c>
+      <c r="Q16" t="s">
+        <v>31</v>
+      </c>
       <c r="R16" t="s">
-        <v>45</v>
-      </c>
-      <c r="S16" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="T16" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="U16" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="V16" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:22">
@@ -4111,28 +4092,22 @@
       <c r="K17" t="s">
         <v>22</v>
       </c>
-      <c r="L17" t="s">
-        <v>22</v>
-      </c>
-      <c r="M17" t="s">
-        <v>22</v>
-      </c>
-      <c r="N17" t="s">
-        <v>22</v>
-      </c>
       <c r="O17" t="s">
         <v>22</v>
       </c>
       <c r="Q17" t="s">
         <v>22</v>
       </c>
-      <c r="R17" t="s">
-        <v>22</v>
-      </c>
       <c r="S17" t="s">
         <v>22</v>
       </c>
       <c r="T17" t="s">
+        <v>22</v>
+      </c>
+      <c r="U17" t="s">
+        <v>22</v>
+      </c>
+      <c r="V17" t="s">
         <v>22</v>
       </c>
     </row>
@@ -4155,47 +4130,41 @@
       <c r="E18" t="s">
         <v>26</v>
       </c>
-      <c r="F18" t="s">
-        <v>24</v>
-      </c>
       <c r="G18" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="H18" t="s">
-        <v>24</v>
+        <v>45</v>
+      </c>
+      <c r="I18" t="s">
+        <v>45</v>
       </c>
       <c r="J18" t="s">
+        <v>40</v>
+      </c>
+      <c r="K18" t="s">
+        <v>42</v>
+      </c>
+      <c r="N18" t="s">
+        <v>25</v>
+      </c>
+      <c r="O18" t="s">
+        <v>25</v>
+      </c>
+      <c r="P18" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>23</v>
+      </c>
+      <c r="R18" t="s">
+        <v>22</v>
+      </c>
+      <c r="T18" t="s">
         <v>45</v>
       </c>
-      <c r="K18" t="s">
-        <v>44</v>
-      </c>
-      <c r="L18" t="s">
-        <v>40</v>
-      </c>
-      <c r="M18" t="s">
-        <v>40</v>
-      </c>
-      <c r="N18" t="s">
-        <v>40</v>
-      </c>
-      <c r="P18" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>41</v>
-      </c>
-      <c r="R18" t="s">
-        <v>40</v>
-      </c>
-      <c r="S18" t="s">
-        <v>41</v>
-      </c>
-      <c r="T18" t="s">
-        <v>41</v>
-      </c>
       <c r="V18" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19" spans="1:22">
@@ -4224,37 +4193,37 @@
         <v>25</v>
       </c>
       <c r="J19" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K19" t="s">
         <v>26</v>
       </c>
       <c r="L19" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="N19" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="O19" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="P19" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="Q19" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="R19" t="s">
-        <v>25</v>
+        <v>42</v>
       </c>
       <c r="T19" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="U19" t="s">
+        <v>42</v>
+      </c>
+      <c r="V19" t="s">
         <v>41</v>
-      </c>
-      <c r="V19" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:22">
@@ -4332,28 +4301,25 @@
       <c r="I21" t="s">
         <v>36</v>
       </c>
-      <c r="J21" t="s">
-        <v>36</v>
-      </c>
       <c r="K21" t="s">
         <v>36</v>
       </c>
       <c r="L21" t="s">
         <v>36</v>
       </c>
+      <c r="M21" t="s">
+        <v>36</v>
+      </c>
       <c r="N21" t="s">
         <v>36</v>
       </c>
       <c r="O21" t="s">
         <v>36</v>
       </c>
-      <c r="P21" t="s">
-        <v>36</v>
-      </c>
       <c r="Q21" t="s">
         <v>36</v>
       </c>
-      <c r="R21" t="s">
+      <c r="S21" t="s">
         <v>36</v>
       </c>
       <c r="T21" t="s">
@@ -4397,31 +4363,34 @@
       <c r="I22" t="s">
         <v>29</v>
       </c>
-      <c r="J22" t="s">
-        <v>29</v>
-      </c>
       <c r="K22" t="s">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="L22" t="s">
         <v>46</v>
       </c>
+      <c r="M22" t="s">
+        <v>46</v>
+      </c>
       <c r="N22" t="s">
         <v>46</v>
       </c>
       <c r="O22" t="s">
         <v>46</v>
       </c>
-      <c r="P22" t="s">
-        <v>46</v>
-      </c>
       <c r="Q22" t="s">
         <v>46</v>
       </c>
       <c r="R22" t="s">
         <v>46</v>
       </c>
+      <c r="S22" t="s">
+        <v>46</v>
+      </c>
       <c r="T22" t="s">
+        <v>46</v>
+      </c>
+      <c r="U22" t="s">
         <v>46</v>
       </c>
     </row>
@@ -4442,52 +4411,49 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H23" t="s">
-        <v>32</v>
-      </c>
-      <c r="I23" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J23" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K23" t="s">
         <v>33</v>
       </c>
+      <c r="L23" t="s">
+        <v>31</v>
+      </c>
       <c r="M23" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="N23" t="s">
         <v>31</v>
       </c>
-      <c r="O23" t="s">
-        <v>29</v>
-      </c>
       <c r="P23" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q23" t="s">
-        <v>33</v>
+        <v>32</v>
+      </c>
+      <c r="R23" t="s">
+        <v>32</v>
       </c>
       <c r="S23" t="s">
         <v>32</v>
       </c>
-      <c r="T23" t="s">
-        <v>33</v>
-      </c>
       <c r="U23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="V23" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:22">
@@ -4510,40 +4476,46 @@
         <v>43</v>
       </c>
       <c r="F24" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I24" t="s">
-        <v>43</v>
-      </c>
-      <c r="K24" t="s">
         <v>39</v>
       </c>
       <c r="L24" t="s">
-        <v>44</v>
+        <v>25</v>
       </c>
       <c r="M24" t="s">
-        <v>39</v>
+        <v>25</v>
+      </c>
+      <c r="N24" t="s">
+        <v>24</v>
       </c>
       <c r="O24" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>42</v>
+        <v>21</v>
+      </c>
+      <c r="P24" t="s">
+        <v>20</v>
+      </c>
+      <c r="R24" t="s">
+        <v>26</v>
+      </c>
+      <c r="S24" t="s">
+        <v>21</v>
       </c>
       <c r="T24" t="s">
         <v>23</v>
       </c>
       <c r="U24" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="V24" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:22">
@@ -4566,7 +4538,7 @@
         <v>42</v>
       </c>
       <c r="F25" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G25" t="s">
         <v>42</v>
@@ -4574,32 +4546,29 @@
       <c r="H25" t="s">
         <v>42</v>
       </c>
-      <c r="I25" t="s">
+      <c r="J25" t="s">
         <v>42</v>
       </c>
-      <c r="L25" t="s">
+      <c r="M25" t="s">
+        <v>20</v>
+      </c>
+      <c r="N25" t="s">
         <v>21</v>
       </c>
-      <c r="M25" t="s">
+      <c r="O25" t="s">
+        <v>23</v>
+      </c>
+      <c r="P25" t="s">
         <v>25</v>
       </c>
-      <c r="N25" t="s">
-        <v>26</v>
-      </c>
-      <c r="O25" t="s">
+      <c r="Q25" t="s">
         <v>25</v>
       </c>
-      <c r="P25" t="s">
-        <v>20</v>
-      </c>
-      <c r="R25" t="s">
-        <v>43</v>
-      </c>
       <c r="S25" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="T25" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="U25" t="s">
         <v>39</v>
@@ -4628,43 +4597,43 @@
         <v>44</v>
       </c>
       <c r="F26" t="s">
-        <v>45</v>
-      </c>
-      <c r="I26" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" t="s">
+        <v>39</v>
+      </c>
+      <c r="H26" t="s">
+        <v>39</v>
+      </c>
+      <c r="J26" t="s">
+        <v>39</v>
+      </c>
+      <c r="M26" t="s">
+        <v>22</v>
+      </c>
+      <c r="N26" t="s">
+        <v>22</v>
+      </c>
+      <c r="O26" t="s">
+        <v>24</v>
+      </c>
+      <c r="P26" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q26" t="s">
         <v>21</v>
       </c>
-      <c r="J26" t="s">
-        <v>26</v>
-      </c>
-      <c r="K26" t="s">
-        <v>24</v>
-      </c>
-      <c r="L26" t="s">
-        <v>24</v>
-      </c>
-      <c r="M26" t="s">
-        <v>26</v>
-      </c>
-      <c r="O26" t="s">
-        <v>21</v>
-      </c>
-      <c r="P26" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>26</v>
-      </c>
-      <c r="R26" t="s">
-        <v>26</v>
-      </c>
       <c r="S26" t="s">
-        <v>24</v>
+        <v>43</v>
+      </c>
+      <c r="T26" t="s">
+        <v>41</v>
       </c>
       <c r="U26" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="V26" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="27" spans="1:22">
@@ -4742,30 +4711,27 @@
       <c r="I28" t="s">
         <v>46</v>
       </c>
-      <c r="J28" t="s">
-        <v>46</v>
-      </c>
-      <c r="K28" t="s">
-        <v>28</v>
-      </c>
       <c r="L28" t="s">
         <v>30</v>
       </c>
+      <c r="M28" t="s">
+        <v>28</v>
+      </c>
       <c r="N28" t="s">
         <v>30</v>
       </c>
       <c r="O28" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="P28" t="s">
-        <v>30</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="R28" t="s">
         <v>30</v>
       </c>
+      <c r="S28" t="s">
+        <v>30</v>
+      </c>
       <c r="T28" t="s">
         <v>30</v>
       </c>
@@ -4773,7 +4739,7 @@
         <v>30</v>
       </c>
       <c r="V28" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" spans="1:22">
@@ -4793,49 +4759,49 @@
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="F29" t="s">
         <v>31</v>
       </c>
       <c r="G29" t="s">
+        <v>34</v>
+      </c>
+      <c r="H29" t="s">
+        <v>34</v>
+      </c>
+      <c r="I29" t="s">
         <v>31</v>
       </c>
-      <c r="H29" t="s">
-        <v>31</v>
-      </c>
-      <c r="I29" t="s">
-        <v>34</v>
-      </c>
       <c r="K29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="M29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="N29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Q29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="R29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="S29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="T29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="U29" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="30" spans="1:22">
@@ -4854,47 +4820,44 @@
         <f>SUM(SUM(((SUMPRODUCT((Cronograma!C$2:C$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!D$2:D$30=$A30)*(Cronograma!$B$2:$B$30=FALSE))&gt;0)),(((SUMPRODUCT((Cronograma!D$2:D$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!C$2:C$30=$A30)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!D$2:D$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!E$2:E$30=$A30)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!E$2:E$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!D$2:D$30=$A30)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!E$2:E$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!F$2:F$30=$A30)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!F$2:F$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!E$2:E$30=$A30)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!F$2:F$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!G$2:G$30=$A30)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!G$2:G$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!F$2:F$30=$A30)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!G$2:G$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!H$2:H$30=$A30)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!H$2:H$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!G$2:G$30=$A30)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!H$2:H$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!I$2:I$30=$A30)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!I$2:I$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!H$2:H$30=$A30)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!I$2:I$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!J$2:J$30=$A30)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!J$2:J$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!I$2:I$30=$A30)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!J$2:J$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!K$2:K$30=$A30)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!K$2:K$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!J$2:J$30=$A30)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!K$2:K$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!L$2:L$30=$A30)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!L$2:L$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!K$2:K$30=$A30)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!L$2:L$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!M$2:M$30=$A30)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!M$2:M$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!L$2:L$30=$A30)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!M$2:M$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!N$2:N$30=$A30)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!N$2:N$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!M$2:M$30=$A30)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!N$2:N$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!O$2:O$30=$A30)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!O$2:O$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!N$2:N$30=$A30)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!O$2:O$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!P$2:P$30=$A30)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!P$2:P$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!O$2:O$30=$A30)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!P$2:P$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!Q$2:Q$30=$A30)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!Q$2:Q$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!P$2:P$30=$A30)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!Q$2:Q$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!R$2:R$30=$A30)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0)),SUM((((SUMPRODUCT((Cronograma!R$2:R$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!Q$2:Q$30=$A30)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!R$2:R$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!S$2:S$30=$A30)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!S$2:S$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!R$2:R$30=$A30)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!S$2:S$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!T$2:T$30=$A30)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),((SUMPRODUCT((Cronograma!T$2:T$30=$A30)*1)=0)*NOT(SUMPRODUCT((Cronograma!S$2:S$30=$A30)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))))</f>
         <v>0</v>
       </c>
-      <c r="E30" t="s">
-        <v>34</v>
+      <c r="F30" t="s">
+        <v>24</v>
       </c>
       <c r="G30" t="s">
-        <v>45</v>
-      </c>
-      <c r="H30" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="I30" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="J30" t="s">
         <v>47</v>
       </c>
       <c r="K30" t="s">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="L30" t="s">
+        <v>41</v>
       </c>
       <c r="M30" t="s">
-        <v>43</v>
-      </c>
-      <c r="N30" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="O30" t="s">
-        <v>43</v>
-      </c>
-      <c r="P30" t="s">
-        <v>40</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>47</v>
+        <v>41</v>
+      </c>
+      <c r="R30" t="s">
+        <v>23</v>
+      </c>
+      <c r="S30" t="s">
+        <v>25</v>
       </c>
       <c r="T30" t="s">
         <v>25</v>
       </c>
       <c r="U30" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="V30" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:22">
@@ -4914,46 +4877,40 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
+        <v>41</v>
+      </c>
+      <c r="I31" t="s">
         <v>34</v>
-      </c>
-      <c r="G31" t="s">
-        <v>34</v>
-      </c>
-      <c r="H31" t="s">
-        <v>34</v>
-      </c>
-      <c r="I31" t="s">
-        <v>26</v>
       </c>
       <c r="J31" t="s">
         <v>34</v>
       </c>
+      <c r="K31" t="s">
+        <v>34</v>
+      </c>
       <c r="L31" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="M31" t="s">
-        <v>34</v>
-      </c>
-      <c r="N31" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="O31" t="s">
-        <v>34</v>
+        <v>43</v>
       </c>
       <c r="P31" t="s">
-        <v>34</v>
+        <v>47</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>42</v>
       </c>
       <c r="R31" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="S31" t="s">
-        <v>47</v>
-      </c>
-      <c r="T31" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="U31" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="V31" t="s">
         <v>47</v>
@@ -4990,9 +4947,6 @@
       <c r="I32" t="s">
         <v>38</v>
       </c>
-      <c r="J32" t="s">
-        <v>38</v>
-      </c>
       <c r="K32" t="s">
         <v>38</v>
       </c>
@@ -5008,9 +4962,6 @@
       <c r="O32" t="s">
         <v>38</v>
       </c>
-      <c r="P32" t="s">
-        <v>38</v>
-      </c>
       <c r="Q32" t="s">
         <v>38</v>
       </c>
@@ -5024,9 +4975,6 @@
         <v>38</v>
       </c>
       <c r="U32" t="s">
-        <v>38</v>
-      </c>
-      <c r="V32" t="s">
         <v>38</v>
       </c>
     </row>
@@ -5050,7 +4998,7 @@
         <v>40</v>
       </c>
       <c r="F33" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G33" t="s">
         <v>40</v>
@@ -5061,20 +5009,23 @@
       <c r="I33" t="s">
         <v>40</v>
       </c>
-      <c r="K33" t="s">
-        <v>45</v>
-      </c>
       <c r="L33" t="s">
-        <v>43</v>
+        <v>24</v>
+      </c>
+      <c r="M33" t="s">
+        <v>26</v>
       </c>
       <c r="N33" t="s">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="O33" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="P33" t="s">
-        <v>42</v>
+        <v>23</v>
+      </c>
+      <c r="R33" t="s">
+        <v>25</v>
       </c>
       <c r="S33" t="s">
         <v>26</v>
@@ -5083,10 +5034,10 @@
         <v>26</v>
       </c>
       <c r="U33" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="V33" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="34" spans="1:22">
@@ -5109,67 +5060,161 @@
         <v>41</v>
       </c>
       <c r="F34" t="s">
+        <v>45</v>
+      </c>
+      <c r="I34" t="s">
+        <v>26</v>
+      </c>
+      <c r="J34" t="s">
+        <v>26</v>
+      </c>
+      <c r="K34" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" t="s">
+        <v>21</v>
+      </c>
+      <c r="M34" t="s">
+        <v>21</v>
+      </c>
+      <c r="O34" t="s">
+        <v>39</v>
+      </c>
+      <c r="P34" t="s">
         <v>43</v>
       </c>
-      <c r="G34" t="s">
-        <v>43</v>
-      </c>
-      <c r="H34" t="s">
-        <v>43</v>
-      </c>
-      <c r="J34" t="s">
-        <v>39</v>
-      </c>
-      <c r="K34" t="s">
+      <c r="Q34" t="s">
+        <v>45</v>
+      </c>
+      <c r="R34" t="s">
         <v>41</v>
       </c>
-      <c r="L34" t="s">
-        <v>41</v>
-      </c>
-      <c r="N34" t="s">
-        <v>41</v>
-      </c>
-      <c r="O34" t="s">
-        <v>40</v>
-      </c>
-      <c r="P34" t="s">
-        <v>39</v>
-      </c>
       <c r="S34" t="s">
-        <v>25</v>
-      </c>
-      <c r="T34" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="U34" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="V34" t="s">
-        <v>20</v>
+        <v>44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22">
+      <c r="A35" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35">
+        <f>SUMPRODUCT((Cronograma!B2:B30=FALSE) * (COUNTIF(E35:V35, Cronograma!A2:A30)))</f>
+        <v>0</v>
+      </c>
+      <c r="C35">
+        <f>SUMPRODUCT((Cronograma!B2:B30=TRUE) * (COUNTIF(E35:V35, Cronograma!A2:A30)))</f>
+        <v>0</v>
+      </c>
+      <c r="D35">
+        <f>SUM(SUM(((SUMPRODUCT((Cronograma!C$2:C$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!D$2:D$30=$A35)*(Cronograma!$B$2:$B$30=FALSE))&gt;0)),(((SUMPRODUCT((Cronograma!D$2:D$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!C$2:C$30=$A35)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!D$2:D$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!E$2:E$30=$A35)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!E$2:E$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!D$2:D$30=$A35)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!E$2:E$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!F$2:F$30=$A35)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!F$2:F$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!E$2:E$30=$A35)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!F$2:F$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!G$2:G$30=$A35)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!G$2:G$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!F$2:F$30=$A35)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!G$2:G$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!H$2:H$30=$A35)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!H$2:H$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!G$2:G$30=$A35)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!H$2:H$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!I$2:I$30=$A35)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!I$2:I$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!H$2:H$30=$A35)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!I$2:I$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!J$2:J$30=$A35)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!J$2:J$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!I$2:I$30=$A35)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!J$2:J$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!K$2:K$30=$A35)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!K$2:K$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!J$2:J$30=$A35)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!K$2:K$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!L$2:L$30=$A35)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!L$2:L$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!K$2:K$30=$A35)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!L$2:L$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!M$2:M$30=$A35)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!M$2:M$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!L$2:L$30=$A35)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!M$2:M$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!N$2:N$30=$A35)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!N$2:N$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!M$2:M$30=$A35)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!N$2:N$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!O$2:O$30=$A35)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!O$2:O$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!N$2:N$30=$A35)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!O$2:O$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!P$2:P$30=$A35)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!P$2:P$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!O$2:O$30=$A35)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!P$2:P$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!Q$2:Q$30=$A35)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!Q$2:Q$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!P$2:P$30=$A35)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!Q$2:Q$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!R$2:R$30=$A35)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0)),SUM((((SUMPRODUCT((Cronograma!R$2:R$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!Q$2:Q$30=$A35)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!R$2:R$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!S$2:S$30=$A35)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!S$2:S$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!R$2:R$30=$A35)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!S$2:S$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!T$2:T$30=$A35)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),((SUMPRODUCT((Cronograma!T$2:T$30=$A35)*1)=0)*NOT(SUMPRODUCT((Cronograma!S$2:S$30=$A35)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))))</f>
+        <v>0</v>
+      </c>
+      <c r="F35" t="s">
+        <v>33</v>
+      </c>
+      <c r="G35" t="s">
+        <v>32</v>
+      </c>
+      <c r="H35" t="s">
+        <v>31</v>
+      </c>
+      <c r="I35" t="s">
+        <v>33</v>
+      </c>
+      <c r="J35" t="s">
+        <v>28</v>
+      </c>
+      <c r="L35" t="s">
+        <v>33</v>
+      </c>
+      <c r="M35" t="s">
+        <v>33</v>
+      </c>
+      <c r="N35" t="s">
+        <v>32</v>
+      </c>
+      <c r="O35" t="s">
+        <v>32</v>
+      </c>
+      <c r="P35" t="s">
+        <v>32</v>
+      </c>
+      <c r="R35" t="s">
+        <v>36</v>
+      </c>
+      <c r="S35" t="s">
+        <v>33</v>
+      </c>
+      <c r="T35" t="s">
+        <v>32</v>
+      </c>
+      <c r="U35" t="s">
+        <v>32</v>
+      </c>
+      <c r="V35" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22">
+      <c r="A36" t="s">
+        <v>87</v>
+      </c>
+      <c r="B36">
+        <f>SUMPRODUCT((Cronograma!B2:B30=FALSE) * (COUNTIF(E36:V36, Cronograma!A2:A30)))</f>
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <f>SUMPRODUCT((Cronograma!B2:B30=TRUE) * (COUNTIF(E36:V36, Cronograma!A2:A30)))</f>
+        <v>0</v>
+      </c>
+      <c r="D36">
+        <f>SUM(SUM(((SUMPRODUCT((Cronograma!C$2:C$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!D$2:D$30=$A36)*(Cronograma!$B$2:$B$30=FALSE))&gt;0)),(((SUMPRODUCT((Cronograma!D$2:D$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!C$2:C$30=$A36)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!D$2:D$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!E$2:E$30=$A36)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!E$2:E$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!D$2:D$30=$A36)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!E$2:E$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!F$2:F$30=$A36)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!F$2:F$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!E$2:E$30=$A36)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!F$2:F$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!G$2:G$30=$A36)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!G$2:G$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!F$2:F$30=$A36)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!G$2:G$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!H$2:H$30=$A36)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!H$2:H$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!G$2:G$30=$A36)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!H$2:H$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!I$2:I$30=$A36)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!I$2:I$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!H$2:H$30=$A36)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!I$2:I$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!J$2:J$30=$A36)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!J$2:J$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!I$2:I$30=$A36)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!J$2:J$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!K$2:K$30=$A36)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!K$2:K$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!J$2:J$30=$A36)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!K$2:K$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!L$2:L$30=$A36)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!L$2:L$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!K$2:K$30=$A36)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!L$2:L$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!M$2:M$30=$A36)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!M$2:M$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!L$2:L$30=$A36)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!M$2:M$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!N$2:N$30=$A36)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!N$2:N$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!M$2:M$30=$A36)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!N$2:N$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!O$2:O$30=$A36)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!O$2:O$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!N$2:N$30=$A36)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!O$2:O$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!P$2:P$30=$A36)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!P$2:P$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!O$2:O$30=$A36)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!P$2:P$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!Q$2:Q$30=$A36)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!Q$2:Q$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!P$2:P$30=$A36)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!Q$2:Q$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!R$2:R$30=$A36)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0)),SUM((((SUMPRODUCT((Cronograma!R$2:R$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!Q$2:Q$30=$A36)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!R$2:R$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!S$2:S$30=$A36)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),(((SUMPRODUCT((Cronograma!S$2:S$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!R$2:R$30=$A36)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))+((SUMPRODUCT((Cronograma!S$2:S$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!T$2:T$30=$A36)*(Cronograma!$B$2:$B$30=FALSE))&gt;0))&gt;0),((SUMPRODUCT((Cronograma!T$2:T$30=$A36)*1)=0)*NOT(SUMPRODUCT((Cronograma!S$2:S$30=$A36)*(Cronograma!$B$2:$B$30=TRUE))&gt;0))))</f>
+        <v>0</v>
+      </c>
+      <c r="E36" t="s">
+        <v>48</v>
+      </c>
+      <c r="F36" t="s">
+        <v>48</v>
+      </c>
+      <c r="G36" t="s">
+        <v>48</v>
+      </c>
+      <c r="H36" t="s">
+        <v>48</v>
+      </c>
+      <c r="I36" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:B34">
+  <conditionalFormatting sqref="B2:B36">
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C2:C34">
+  <conditionalFormatting sqref="C2:C36">
     <cfRule type="expression" dxfId="2" priority="4">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D34">
+  <conditionalFormatting sqref="D2:D36">
     <cfRule type="expression" dxfId="3" priority="23">
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E34">
+  <conditionalFormatting sqref="E2:E36">
     <cfRule type="expression" dxfId="3" priority="5">
       <formula>OR(AND(ISERROR(MATCH($A2, Cronograma!C$2:C$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!D$2:D$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!D$2:D$30,0))=FALSE))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:V34">
+  <conditionalFormatting sqref="E2:V36">
     <cfRule type="expression" dxfId="1" priority="1">
       <formula>VLOOKUP(E2, Cronograma!$A$2:$B$30, 2, FALSE)=FALSE</formula>
     </cfRule>
@@ -5177,87 +5222,87 @@
       <formula>VLOOKUP(E2, Cronograma!$A$2:$B$30, 2, FALSE)=TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:F34">
+  <conditionalFormatting sqref="F2:F36">
     <cfRule type="expression" dxfId="3" priority="6">
       <formula>OR(AND(ISERROR(MATCH($A2, Cronograma!D$2:D$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!C$2:C$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!C$2:C$30,0))=TRUE))),AND(ISERROR(MATCH($A2, Cronograma!D$2:D$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!E$2:E$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!E$2:E$30,0))=FALSE))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G2:G34">
+  <conditionalFormatting sqref="G2:G36">
     <cfRule type="expression" dxfId="3" priority="7">
       <formula>OR(AND(ISERROR(MATCH($A2, Cronograma!E$2:E$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!D$2:D$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!D$2:D$30,0))=TRUE))),AND(ISERROR(MATCH($A2, Cronograma!E$2:E$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!F$2:F$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!F$2:F$30,0))=FALSE))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H2:H34">
+  <conditionalFormatting sqref="H2:H36">
     <cfRule type="expression" dxfId="3" priority="8">
       <formula>OR(AND(ISERROR(MATCH($A2, Cronograma!F$2:F$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!E$2:E$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!E$2:E$30,0))=TRUE))),AND(ISERROR(MATCH($A2, Cronograma!F$2:F$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!G$2:G$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!G$2:G$30,0))=FALSE))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I34">
+  <conditionalFormatting sqref="I2:I36">
     <cfRule type="expression" dxfId="3" priority="9">
       <formula>OR(AND(ISERROR(MATCH($A2, Cronograma!G$2:G$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!F$2:F$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!F$2:F$30,0))=TRUE))),AND(ISERROR(MATCH($A2, Cronograma!G$2:G$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!H$2:H$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!H$2:H$30,0))=FALSE))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J34">
+  <conditionalFormatting sqref="J2:J36">
     <cfRule type="expression" dxfId="3" priority="10">
       <formula>OR(AND(ISERROR(MATCH($A2, Cronograma!H$2:H$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!G$2:G$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!G$2:G$30,0))=TRUE))),AND(ISERROR(MATCH($A2, Cronograma!H$2:H$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!I$2:I$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!I$2:I$30,0))=FALSE))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K2:K34">
+  <conditionalFormatting sqref="K2:K36">
     <cfRule type="expression" dxfId="3" priority="11">
       <formula>OR(AND(ISERROR(MATCH($A2, Cronograma!I$2:I$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!H$2:H$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!H$2:H$30,0))=TRUE))),AND(ISERROR(MATCH($A2, Cronograma!I$2:I$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!J$2:J$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!J$2:J$30,0))=FALSE))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L34">
+  <conditionalFormatting sqref="L2:L36">
     <cfRule type="expression" dxfId="3" priority="12">
       <formula>OR(AND(ISERROR(MATCH($A2, Cronograma!J$2:J$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!I$2:I$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!I$2:I$30,0))=TRUE))),AND(ISERROR(MATCH($A2, Cronograma!J$2:J$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!K$2:K$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!K$2:K$30,0))=FALSE))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M34">
+  <conditionalFormatting sqref="M2:M36">
     <cfRule type="expression" dxfId="3" priority="13">
       <formula>OR(AND(ISERROR(MATCH($A2, Cronograma!K$2:K$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!J$2:J$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!J$2:J$30,0))=TRUE))),AND(ISERROR(MATCH($A2, Cronograma!K$2:K$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!L$2:L$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!L$2:L$30,0))=FALSE))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="N2:N34">
+  <conditionalFormatting sqref="N2:N36">
     <cfRule type="expression" dxfId="3" priority="14">
       <formula>OR(AND(ISERROR(MATCH($A2, Cronograma!L$2:L$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!K$2:K$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!K$2:K$30,0))=TRUE))),AND(ISERROR(MATCH($A2, Cronograma!L$2:L$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!M$2:M$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!M$2:M$30,0))=FALSE))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O2:O34">
+  <conditionalFormatting sqref="O2:O36">
     <cfRule type="expression" dxfId="3" priority="15">
       <formula>OR(AND(ISERROR(MATCH($A2, Cronograma!M$2:M$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!L$2:L$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!L$2:L$30,0))=TRUE))),AND(ISERROR(MATCH($A2, Cronograma!M$2:M$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!N$2:N$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!N$2:N$30,0))=FALSE))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="P2:P34">
+  <conditionalFormatting sqref="P2:P36">
     <cfRule type="expression" dxfId="3" priority="16">
       <formula>OR(AND(ISERROR(MATCH($A2, Cronograma!N$2:N$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!M$2:M$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!M$2:M$30,0))=TRUE))),AND(ISERROR(MATCH($A2, Cronograma!N$2:N$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!O$2:O$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!O$2:O$30,0))=FALSE))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Q2:Q34">
+  <conditionalFormatting sqref="Q2:Q36">
     <cfRule type="expression" dxfId="3" priority="17">
       <formula>OR(AND(ISERROR(MATCH($A2, Cronograma!O$2:O$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!N$2:N$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!N$2:N$30,0))=TRUE))),AND(ISERROR(MATCH($A2, Cronograma!O$2:O$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!P$2:P$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!P$2:P$30,0))=FALSE))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R2:R34">
+  <conditionalFormatting sqref="R2:R36">
     <cfRule type="expression" dxfId="3" priority="18">
       <formula>OR(AND(ISERROR(MATCH($A2, Cronograma!P$2:P$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!O$2:O$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!O$2:O$30,0))=TRUE))),AND(ISERROR(MATCH($A2, Cronograma!P$2:P$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!Q$2:Q$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!Q$2:Q$30,0))=FALSE))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S34">
+  <conditionalFormatting sqref="S2:S36">
     <cfRule type="expression" dxfId="3" priority="19">
       <formula>OR(AND(ISERROR(MATCH($A2, Cronograma!Q$2:Q$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!P$2:P$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!P$2:P$30,0))=TRUE))),AND(ISERROR(MATCH($A2, Cronograma!Q$2:Q$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!R$2:R$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!R$2:R$30,0))=FALSE))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T2:T34">
+  <conditionalFormatting sqref="T2:T36">
     <cfRule type="expression" dxfId="3" priority="20">
       <formula>OR(AND(ISERROR(MATCH($A2, Cronograma!R$2:R$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!Q$2:Q$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!Q$2:Q$30,0))=TRUE))),AND(ISERROR(MATCH($A2, Cronograma!R$2:R$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!S$2:S$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!S$2:S$30,0))=FALSE))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="U2:U34">
+  <conditionalFormatting sqref="U2:U36">
     <cfRule type="expression" dxfId="3" priority="21">
       <formula>OR(AND(ISERROR(MATCH($A2, Cronograma!S$2:S$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!R$2:R$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!R$2:R$30,0))=TRUE))),AND(ISERROR(MATCH($A2, Cronograma!S$2:S$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!T$2:T$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!T$2:T$30,0))=FALSE))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V2:V34">
+  <conditionalFormatting sqref="V2:V36">
     <cfRule type="expression" dxfId="3" priority="22">
       <formula>OR(AND(ISERROR(MATCH($A2, Cronograma!T$2:T$30, 0)), NOT(IF(ISERROR(MATCH($A2,Cronograma!S$2:S$30,0)),FALSE,INDEX(Cronograma!$B$2:$B$30,MATCH($A2,Cronograma!S$2:S$30,0))=TRUE))))</formula>
     </cfRule>
